--- a/data/axe1/ALTERMAP_2026_Vision_du_Monde_SMA_codes.xlsx
+++ b/data/axe1/ALTERMAP_2026_Vision_du_Monde_SMA_codes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/claudegrasland1/worldregio/altermap/data/axe1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC4F12D-307D-1645-A2FB-337060DC969A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C648B3CC-7E90-DA4D-9099-869B36667446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="19420" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ALTERMAP 2026 - Vision du Monde" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4185" uniqueCount="1600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4185" uniqueCount="1601">
   <si>
     <t>start</t>
   </si>
@@ -3319,1507 +3319,1510 @@
     <t>uuid:91de6a8a-32c1-4ff6-a3ed-9d219bd9a07f</t>
   </si>
   <si>
+    <t>N1 N2 N3 N4 N5</t>
+  </si>
+  <si>
+    <t>monnaie commune</t>
+  </si>
+  <si>
+    <t>union européenne</t>
+  </si>
+  <si>
+    <t>centre</t>
+  </si>
+  <si>
+    <t>occident</t>
+  </si>
+  <si>
+    <t>littoral</t>
+  </si>
+  <si>
+    <t>pays du sud</t>
+  </si>
+  <si>
+    <t>équateur</t>
+  </si>
+  <si>
+    <t>REG_CON_EUR_centr</t>
+  </si>
+  <si>
+    <t>ef9f8d7a-dee1-4f84-b7e0-292d51cc4d9c</t>
+  </si>
+  <si>
+    <t>uuid:ef9f8d7a-dee1-4f84-b7e0-292d51cc4d9c</t>
+  </si>
+  <si>
+    <t>ara</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>OMN</t>
+  </si>
+  <si>
+    <t>UKR</t>
+  </si>
+  <si>
+    <t>COD</t>
+  </si>
+  <si>
+    <t>Nord</t>
+  </si>
+  <si>
+    <t>domination</t>
+  </si>
+  <si>
+    <t>pouvoir</t>
+  </si>
+  <si>
+    <t>olive</t>
+  </si>
+  <si>
+    <t>joie</t>
+  </si>
+  <si>
+    <t>histoire</t>
+  </si>
+  <si>
+    <t>mémoire</t>
+  </si>
+  <si>
+    <t>REG_CON_EUR_south</t>
+  </si>
+  <si>
+    <t>pays slaves</t>
+  </si>
+  <si>
+    <t>pays desi (?)</t>
+  </si>
+  <si>
+    <t>illisible</t>
+  </si>
+  <si>
+    <t>654e1025-e902-4382-b13a-67b4d02784da</t>
+  </si>
+  <si>
+    <t>uuid:654e1025-e902-4382-b13a-67b4d02784da</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>FIN</t>
+  </si>
+  <si>
+    <t>MTQ</t>
+  </si>
+  <si>
+    <t>froid</t>
+  </si>
+  <si>
+    <t>colonisateur</t>
+  </si>
+  <si>
+    <t>REG_CON_EUR_north</t>
+  </si>
+  <si>
+    <t>8f54acc8-a6d4-47ff-b972-8b3ad55e3fd7</t>
+  </si>
+  <si>
+    <t>uuid:8f54acc8-a6d4-47ff-b972-8b3ad55e3fd7</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>construction</t>
+  </si>
+  <si>
+    <t>eurocentrisme</t>
+  </si>
+  <si>
+    <t>antiquité héritage</t>
+  </si>
+  <si>
+    <t>interface</t>
+  </si>
+  <si>
+    <t>médiatisation</t>
+  </si>
+  <si>
+    <t>penseurs, hommes de lettre, négritude</t>
+  </si>
+  <si>
+    <t>Europe du Nord + Groeënland</t>
+  </si>
+  <si>
+    <t>Moyen et extrême Orient</t>
+  </si>
+  <si>
+    <t>Russie et une partie de l'Asie centrale</t>
+  </si>
+  <si>
+    <t>Asie du Sud / Inde</t>
+  </si>
+  <si>
+    <t>76690887-afb7-4c87-bb58-8a008a9d68b8</t>
+  </si>
+  <si>
+    <t>uuid:76690887-afb7-4c87-bb58-8a008a9d68b8</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>CMR</t>
+  </si>
+  <si>
+    <t>UZB</t>
+  </si>
+  <si>
+    <t>extrêmes droites</t>
+  </si>
+  <si>
+    <t>mauvais temps</t>
+  </si>
+  <si>
+    <t>multiculturelle</t>
+  </si>
+  <si>
+    <t>migrants</t>
+  </si>
+  <si>
+    <t>ressources naturelles</t>
+  </si>
+  <si>
+    <t>Moyen / Extrême Orient</t>
+  </si>
+  <si>
+    <t>hotlia3@gmail.com</t>
+  </si>
+  <si>
+    <t>c74041e0-3dc3-41a5-aff0-e43f82c35c76</t>
+  </si>
+  <si>
+    <t>uuid:c74041e0-3dc3-41a5-aff0-e43f82c35c76</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>fon</t>
+  </si>
+  <si>
+    <t>BFA</t>
+  </si>
+  <si>
+    <t>GHA</t>
+  </si>
+  <si>
+    <t>N1 N3 N4</t>
+  </si>
+  <si>
+    <t>KWT</t>
+  </si>
+  <si>
+    <t>SOM</t>
+  </si>
+  <si>
+    <t>continent européen</t>
+  </si>
+  <si>
+    <t>région européenne</t>
+  </si>
+  <si>
+    <t>espace schengen</t>
+  </si>
+  <si>
+    <t>climat méditerranéen</t>
+  </si>
+  <si>
+    <t>route commercial</t>
+  </si>
+  <si>
+    <t>flux</t>
+  </si>
+  <si>
+    <t>continent africain</t>
+  </si>
+  <si>
+    <t>Sahara</t>
+  </si>
+  <si>
+    <t>972d65de-832f-4327-9c8c-d97031e76a38</t>
+  </si>
+  <si>
+    <t>uuid:972d65de-832f-4327-9c8c-d97031e76a38</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>N1 N2 N3 N4</t>
+  </si>
+  <si>
+    <t>DZA</t>
+  </si>
+  <si>
+    <t>colonie</t>
+  </si>
+  <si>
+    <t>puissance historique</t>
+  </si>
+  <si>
+    <t>vaste</t>
+  </si>
+  <si>
+    <t>diversité frontalière</t>
+  </si>
+  <si>
+    <t>beau</t>
+  </si>
+  <si>
+    <t>a9b7212d-f30d-4b04-af69-60537ff38567</t>
+  </si>
+  <si>
+    <t>uuid:a9b7212d-f30d-4b04-af69-60537ff38567</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t>MDV</t>
+  </si>
+  <si>
+    <t>NER</t>
+  </si>
+  <si>
+    <t>Espagne</t>
+  </si>
+  <si>
+    <t>Italie</t>
+  </si>
+  <si>
+    <t>Belgique</t>
+  </si>
+  <si>
+    <t>Allemagne</t>
+  </si>
+  <si>
+    <t>Afrique du Sud</t>
+  </si>
+  <si>
+    <t>Nigéria</t>
+  </si>
+  <si>
+    <t>Mali</t>
+  </si>
+  <si>
+    <t>Egypte</t>
+  </si>
+  <si>
+    <t>0df6765d-b313-4f73-bbcd-50111d64c4de</t>
+  </si>
+  <si>
+    <t>uuid:0df6765d-b313-4f73-bbcd-50111d64c4de</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>HTI</t>
+  </si>
+  <si>
+    <t>POL</t>
+  </si>
+  <si>
+    <t>faible</t>
+  </si>
+  <si>
+    <t>utopie</t>
+  </si>
+  <si>
+    <t>narcotraffic</t>
+  </si>
+  <si>
+    <t>potentiel</t>
+  </si>
+  <si>
+    <t>dictateurs</t>
+  </si>
+  <si>
+    <t>guerre / conflits</t>
+  </si>
+  <si>
+    <t>guerres éternelles</t>
+  </si>
+  <si>
+    <t>puissances orientales</t>
+  </si>
+  <si>
+    <t>bloc de l'humaisme</t>
+  </si>
+  <si>
+    <t>démocratie 155 mm</t>
+  </si>
+  <si>
+    <t>Drigs and Soy</t>
+  </si>
+  <si>
+    <t>scooters and t-shirts</t>
+  </si>
+  <si>
+    <t>the great COAL reef.</t>
+  </si>
+  <si>
+    <t>"chez eux"</t>
+  </si>
+  <si>
+    <t>ping pong</t>
+  </si>
+  <si>
+    <t>racists</t>
+  </si>
+  <si>
+    <t>they exists</t>
+  </si>
+  <si>
+    <t>AK-47, CIA, Wonderland</t>
+  </si>
+  <si>
+    <t>42947143-a948-49a7-bdcc-94cd8dc91286</t>
+  </si>
+  <si>
+    <t>uuid:42947143-a948-49a7-bdcc-94cd8dc91286</t>
+  </si>
+  <si>
+    <t>SMA-GR4</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>LIE</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>N1 N2 X</t>
+  </si>
+  <si>
+    <t>la région à côté</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
+    <t>continent</t>
+  </si>
+  <si>
+    <t>démocrates</t>
+  </si>
+  <si>
+    <t>Erasmus</t>
+  </si>
+  <si>
+    <t>plats</t>
+  </si>
+  <si>
+    <t>pêche</t>
+  </si>
+  <si>
+    <t>au milieu des terres</t>
+  </si>
+  <si>
+    <t>Bafoussam</t>
+  </si>
+  <si>
+    <t>Mafé</t>
+  </si>
+  <si>
+    <t>sol rouge</t>
+  </si>
+  <si>
+    <t>Afrique du Sud et de l'Est</t>
+  </si>
+  <si>
+    <t>tony77130@gmail.com</t>
+  </si>
+  <si>
+    <t>38fbb04c-f86d-4866-a34d-a9380c464d3a</t>
+  </si>
+  <si>
+    <t>uuid:38fbb04c-f86d-4866-a34d-a9380c464d3a</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>SVN</t>
+  </si>
+  <si>
+    <t>château</t>
+  </si>
+  <si>
+    <t>liberté</t>
+  </si>
+  <si>
+    <t>empire romain</t>
+  </si>
+  <si>
+    <t>Grèce antique</t>
+  </si>
+  <si>
+    <t>pyramide</t>
+  </si>
+  <si>
+    <t>famine</t>
+  </si>
+  <si>
+    <t>dictature</t>
+  </si>
+  <si>
+    <t>Québec libre</t>
+  </si>
+  <si>
+    <t>REG_CON_ASI_pacif</t>
+  </si>
+  <si>
+    <t>ed4fe0e2-e42f-4f10-a424-631105521e9f</t>
+  </si>
+  <si>
+    <t>uuid:ed4fe0e2-e42f-4f10-a424-631105521e9f</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>N1 N3</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>blanc</t>
+  </si>
+  <si>
+    <t>stable</t>
+  </si>
+  <si>
+    <t>puissance</t>
+  </si>
+  <si>
+    <t>jeune</t>
+  </si>
+  <si>
+    <t>noire</t>
+  </si>
+  <si>
+    <t>ressource</t>
+  </si>
+  <si>
+    <t>conflit , vaste</t>
+  </si>
+  <si>
+    <t>REG_CON_EUR_south_east</t>
+  </si>
+  <si>
+    <t>pierrealexisgavrilenko@gmail.com</t>
+  </si>
+  <si>
+    <t>a8e2bebb-fd37-49ac-8652-dfdfd3fb4464</t>
+  </si>
+  <si>
+    <t>uuid:a17c93f4-35c3-4830-9a30-279353c5f329</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>LBN</t>
+  </si>
+  <si>
+    <t>lois</t>
+  </si>
+  <si>
+    <t>titre de séjour</t>
+  </si>
+  <si>
+    <t>eau</t>
+  </si>
+  <si>
+    <t>sous-développement</t>
+  </si>
+  <si>
+    <t>REG_CON_AMR</t>
+  </si>
+  <si>
+    <t>6b2e2e52-9566-414a-b94f-7eaf58fde5c9</t>
+  </si>
+  <si>
+    <t>uuid:6b2e2e52-9566-414a-b94f-7eaf58fde5c9</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>ROM</t>
+  </si>
+  <si>
+    <t>N1 N3 X</t>
+  </si>
+  <si>
+    <t>Yerevan</t>
+  </si>
+  <si>
+    <t>AZE</t>
+  </si>
+  <si>
+    <t>force, puissance</t>
+  </si>
+  <si>
+    <t>économie</t>
+  </si>
+  <si>
+    <t>traversée</t>
+  </si>
+  <si>
+    <t>dangers</t>
+  </si>
+  <si>
+    <t>côte</t>
+  </si>
+  <si>
+    <t>dictature militaire</t>
+  </si>
+  <si>
+    <t>tribus</t>
+  </si>
+  <si>
+    <t>Caucase / Proche-Orient</t>
+  </si>
+  <si>
+    <t>lois.petrossian@gmail.com</t>
+  </si>
+  <si>
+    <t>Plutôt que les paus de naissance, demander les origines.</t>
+  </si>
+  <si>
+    <t>182b1f2c-dcc8-4ca0-a7e2-05a2d54ed9f7</t>
+  </si>
+  <si>
+    <t>uuid:182b1f2c-dcc8-4ca0-a7e2-05a2d54ed9f7</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>N1 N2 N3 N4 N5 X</t>
+  </si>
+  <si>
+    <t>Cameroun-France métissage</t>
+  </si>
+  <si>
+    <t>chute démographique</t>
+  </si>
+  <si>
+    <t>centre du monde</t>
+  </si>
+  <si>
+    <t>pillage, occident</t>
+  </si>
+  <si>
+    <t>guerres</t>
+  </si>
+  <si>
+    <t>histoire (de sa région)</t>
+  </si>
+  <si>
+    <t>réchauffement climatique</t>
+  </si>
+  <si>
+    <t>ressources premières</t>
+  </si>
+  <si>
+    <t>espoir</t>
+  </si>
+  <si>
+    <t>héritages, conflits</t>
+  </si>
+  <si>
+    <t>Afrique "noire"</t>
+  </si>
+  <si>
+    <t>Océanie du sud</t>
+  </si>
+  <si>
+    <t>Océanie occidentale</t>
+  </si>
+  <si>
+    <t>Russie ? ni Europe, ni Asie, en guerre</t>
+  </si>
+  <si>
+    <t>2def15b5-17ac-4362-97e8-1b19437722ca</t>
+  </si>
+  <si>
+    <t>uuid:2def15b5-17ac-4362-97e8-1b19437722ca</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>guerre historique</t>
+  </si>
+  <si>
+    <t>culture culinaire</t>
+  </si>
+  <si>
+    <t>défis futus</t>
+  </si>
+  <si>
+    <t>chaud</t>
+  </si>
+  <si>
+    <t>savane</t>
+  </si>
+  <si>
+    <t>art tribal</t>
+  </si>
+  <si>
+    <t>empire colonial</t>
+  </si>
+  <si>
+    <t>richesse culturelle</t>
+  </si>
+  <si>
+    <t>Le Monde</t>
+  </si>
+  <si>
+    <t>3dfc76e2-647b-42df-938d-520bff479dac</t>
+  </si>
+  <si>
+    <t>uuid:3dfc76e2-647b-42df-938d-520bff479dac</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>N2 N3 N4</t>
+  </si>
+  <si>
+    <t>perte de vitesse</t>
+  </si>
+  <si>
+    <t>identité</t>
+  </si>
+  <si>
+    <t>vanité</t>
+  </si>
+  <si>
+    <t>défi</t>
+  </si>
+  <si>
+    <t>inondation</t>
+  </si>
+  <si>
+    <t>hurricane</t>
+  </si>
+  <si>
+    <t>bleue</t>
+  </si>
+  <si>
+    <t>tradition</t>
+  </si>
+  <si>
+    <t>avenir</t>
+  </si>
+  <si>
+    <t>lion</t>
+  </si>
+  <si>
+    <t>Monde</t>
+  </si>
+  <si>
+    <t>96f48454-85e4-4b46-8a00-b3afcd3359f7</t>
+  </si>
+  <si>
+    <t>uuid:96f48454-85e4-4b46-8a00-b3afcd3359f7</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>NPL</t>
+  </si>
+  <si>
+    <t>unité</t>
+  </si>
+  <si>
+    <t>projet</t>
+  </si>
+  <si>
+    <t>défis</t>
+  </si>
+  <si>
+    <t>mare nostrum</t>
+  </si>
+  <si>
+    <t>cuisine</t>
+  </si>
+  <si>
+    <t>tristesse</t>
+  </si>
+  <si>
+    <t>inconnu</t>
+  </si>
+  <si>
+    <t>zone tropicale</t>
+  </si>
+  <si>
+    <t>zone subtropicale</t>
+  </si>
+  <si>
+    <t>zone tempérée</t>
+  </si>
+  <si>
+    <t>zone polaire / subpolaire</t>
+  </si>
+  <si>
+    <t>ca71aaa8-369d-4896-a2ad-7221e9826990</t>
+  </si>
+  <si>
+    <t>uuid:ca71aaa8-369d-4896-a2ad-7221e9826990</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>voyage</t>
+  </si>
+  <si>
+    <t>un petit dauphin</t>
+  </si>
+  <si>
+    <t>centralité</t>
+  </si>
+  <si>
+    <t>en développement</t>
+  </si>
+  <si>
+    <t>faune</t>
+  </si>
+  <si>
+    <t>natures</t>
+  </si>
+  <si>
+    <t>56a2b4a5-4d39-4ce2-abd2-66eea92431eb</t>
+  </si>
+  <si>
+    <t>uuid:56a2b4a5-4d39-4ce2-abd2-66eea92431eb</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>température de l'eau</t>
+  </si>
+  <si>
+    <t>beaucoup de monde</t>
+  </si>
+  <si>
+    <t>sourire</t>
+  </si>
+  <si>
+    <t>sécheresse</t>
+  </si>
+  <si>
+    <t>safaris, diversité, animaux, paysages, beauté</t>
+  </si>
+  <si>
+    <t>976c8ea7-30e4-4af9-b171-61503887bb24</t>
+  </si>
+  <si>
+    <t>uuid:976c8ea7-30e4-4af9-b171-61503887bb24</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>GTM</t>
+  </si>
+  <si>
+    <t>guerre froide</t>
+  </si>
+  <si>
+    <t>royaume</t>
+  </si>
+  <si>
+    <t>soft power</t>
+  </si>
+  <si>
+    <t>Gibraltar</t>
+  </si>
+  <si>
+    <t>population</t>
+  </si>
+  <si>
+    <t>préhistoire</t>
+  </si>
+  <si>
+    <t>sahara</t>
+  </si>
+  <si>
+    <t>408f7c1f-5da5-4a59-a1de-3bee328ee2d4</t>
+  </si>
+  <si>
+    <t>uuid:408f7c1f-5da5-4a59-a1de-3bee328ee2d4</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>chancceux</t>
+  </si>
+  <si>
+    <t>cohésion</t>
+  </si>
+  <si>
+    <t>rainistification (?)</t>
+  </si>
+  <si>
+    <t>nature</t>
+  </si>
+  <si>
+    <t>beauté</t>
+  </si>
+  <si>
+    <t>980e233c-9d91-45f3-be71-1ced246c1126</t>
+  </si>
+  <si>
+    <t>uuid:980e233c-9d91-45f3-be71-1ced246c1126</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>voyages</t>
+  </si>
+  <si>
+    <t>villes</t>
+  </si>
+  <si>
+    <t>pollution</t>
+  </si>
+  <si>
+    <t>surconsommation</t>
+  </si>
+  <si>
+    <t>ports</t>
+  </si>
+  <si>
+    <t>animaux</t>
+  </si>
+  <si>
+    <t>8650fa0e-8d2a-40b8-999d-73b93bd18099</t>
+  </si>
+  <si>
+    <t>uuid:8650fa0e-8d2a-40b8-999d-73b93bd18099</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>TCD</t>
+  </si>
+  <si>
+    <t>travail</t>
+  </si>
+  <si>
+    <t>plages</t>
+  </si>
+  <si>
+    <t>nature, forêts</t>
+  </si>
+  <si>
+    <t>f6a68bc5-8ac9-4350-9f40-45c553ae5977</t>
+  </si>
+  <si>
+    <t>uuid:f6a68bc5-8ac9-4350-9f40-45c553ae5977</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>MKD</t>
+  </si>
+  <si>
+    <t>KOS</t>
+  </si>
+  <si>
+    <t>SRB</t>
+  </si>
+  <si>
+    <t>Nords</t>
+  </si>
+  <si>
+    <t>séparation</t>
+  </si>
+  <si>
+    <t>tragédie</t>
+  </si>
+  <si>
+    <t>futur</t>
+  </si>
+  <si>
+    <t>investissement</t>
+  </si>
+  <si>
+    <t>REG_OTH_SEA_atlantic</t>
+  </si>
+  <si>
+    <t>lepape.nils@gmail.com</t>
+  </si>
+  <si>
+    <t>13383b26-6917-4309-912c-7c45922fef3c</t>
+  </si>
+  <si>
+    <t>uuid:13383b26-6917-4309-912c-7c45922fef3c</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>srp</t>
+  </si>
+  <si>
+    <t>religion</t>
+  </si>
+  <si>
+    <t>montagne</t>
+  </si>
+  <si>
+    <t>châteaux</t>
+  </si>
+  <si>
+    <t>football</t>
+  </si>
+  <si>
+    <t>entraide</t>
+  </si>
+  <si>
+    <t>calme</t>
+  </si>
+  <si>
+    <t>beauté, paysage</t>
+  </si>
+  <si>
+    <t>fruits, nourriture fraîche</t>
+  </si>
+  <si>
+    <t>diversité, paysage</t>
+  </si>
+  <si>
+    <t>exotisme</t>
+  </si>
+  <si>
+    <t>Nord riche</t>
+  </si>
+  <si>
+    <t>Océan</t>
+  </si>
+  <si>
+    <t>Asie Sud / Océanie</t>
+  </si>
+  <si>
+    <t>147776f8-ff9c-4149-951b-703dd52342f9</t>
+  </si>
+  <si>
+    <t>uuid:774d985b-af79-4ca3-9d82-d32ce8244293</t>
+  </si>
+  <si>
+    <t>SMA-GR3</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
+    <t>monnaie</t>
+  </si>
+  <si>
+    <t>agriculture</t>
+  </si>
+  <si>
+    <t>divers</t>
+  </si>
+  <si>
+    <t>pauvre</t>
+  </si>
+  <si>
+    <t>pillée</t>
+  </si>
+  <si>
+    <t>STA_NAM_USA</t>
+  </si>
+  <si>
+    <t>démocarties des Nords</t>
+  </si>
+  <si>
+    <t>justinbarrault7@gmail.com</t>
+  </si>
+  <si>
+    <t>a777d387-c97b-4e49-bb5e-51874fba3956</t>
+  </si>
+  <si>
+    <t>uuid:bba89295-293e-4ef5-8b5c-2ff00def4f2e</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>espace Schengen</t>
+  </si>
+  <si>
+    <t>Marseille</t>
+  </si>
+  <si>
+    <t>salade</t>
+  </si>
+  <si>
+    <t>Côte d'azur</t>
+  </si>
+  <si>
+    <t>foutou</t>
+  </si>
+  <si>
+    <t>Maghreb</t>
+  </si>
+  <si>
+    <t>Amérique des "Nords"</t>
+  </si>
+  <si>
+    <t>STA_NAM_BRA</t>
+  </si>
+  <si>
+    <t>Europe de l'Est / Moyen Orient</t>
+  </si>
+  <si>
+    <t>puichaffretjoseph@gmail.com</t>
+  </si>
+  <si>
+    <t>8d6b2038-cb8d-4719-941d-8a5a963e56e4</t>
+  </si>
+  <si>
+    <t>uuid:8d6b2038-cb8d-4719-941d-8a5a963e56e4</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>urd</t>
+  </si>
+  <si>
+    <t>été, vacances</t>
+  </si>
+  <si>
+    <t>morts, noyades</t>
+  </si>
+  <si>
+    <t>inégalitaire</t>
+  </si>
+  <si>
+    <t>très très diverse</t>
+  </si>
+  <si>
+    <t>prospérité</t>
+  </si>
+  <si>
+    <t>colonies</t>
+  </si>
+  <si>
+    <t>557ec1d0-c074-4288-99d9-f9b2656edbf5</t>
+  </si>
+  <si>
+    <t>uuid:a2540619-c477-4d84-88a3-eb3bf4c5d7fe</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>TWN</t>
+  </si>
+  <si>
+    <t>Pays riches</t>
+  </si>
+  <si>
+    <t>Europe / Afrique / Asie</t>
+  </si>
+  <si>
+    <t>Sud</t>
+  </si>
+  <si>
+    <t>néocolonialisme</t>
+  </si>
+  <si>
+    <t>REG_CON_ASI_north</t>
+  </si>
+  <si>
+    <t>3d6eae70-bff9-41a4-8386-f8b5e03ecbb0</t>
+  </si>
+  <si>
+    <t>uuid:3d6eae70-bff9-41a4-8386-f8b5e03ecbb0</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>wol</t>
+  </si>
+  <si>
+    <t>ita</t>
+  </si>
+  <si>
+    <t>pays musulmans</t>
+  </si>
+  <si>
+    <t>Grèce</t>
+  </si>
+  <si>
+    <t>Cameroun</t>
+  </si>
+  <si>
+    <t>Maroc</t>
+  </si>
+  <si>
+    <t>Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>penda.mbaye136@gmail.com</t>
+  </si>
+  <si>
+    <t>46026cae-c90e-4c99-8970-9b116346d617</t>
+  </si>
+  <si>
+    <t>uuid:46026cae-c90e-4c99-8970-9b116346d617</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>maison</t>
+  </si>
+  <si>
+    <t>enjeux</t>
+  </si>
+  <si>
+    <t>abondance</t>
+  </si>
+  <si>
+    <t>huile</t>
+  </si>
+  <si>
+    <t>Barcelonne</t>
+  </si>
+  <si>
+    <t>forêt tropicale</t>
+  </si>
+  <si>
+    <t>inégalités</t>
+  </si>
+  <si>
+    <t>pôle Nord</t>
+  </si>
+  <si>
+    <t>48f69873-75b5-4e98-812f-3cac6d012f4b</t>
+  </si>
+  <si>
+    <t>uuid:48f69873-75b5-4e98-812f-3cac6d012f4b</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>ancien</t>
+  </si>
+  <si>
+    <t>vigne</t>
+  </si>
+  <si>
+    <t>colonisé</t>
+  </si>
+  <si>
+    <t>Asie peuplée</t>
+  </si>
+  <si>
+    <t>8bdeea2d-310d-4c7e-b67f-cad9e70738f3</t>
+  </si>
+  <si>
+    <t>uuid:8bdeea2d-310d-4c7e-b67f-cad9e70738f3</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>déclin</t>
+  </si>
+  <si>
+    <t>fascisme</t>
+  </si>
+  <si>
+    <t>Sicile</t>
+  </si>
+  <si>
+    <t>berceau</t>
+  </si>
+  <si>
+    <t>esclavage</t>
+  </si>
+  <si>
+    <t>exploité</t>
+  </si>
+  <si>
+    <t>Les Nords</t>
+  </si>
+  <si>
+    <t>Les Suds</t>
+  </si>
+  <si>
+    <t>c2557764-e156-4dd2-afd2-fe1ed0325c34</t>
+  </si>
+  <si>
+    <t>uuid:c2557764-e156-4dd2-afd2-fe1ed0325c34</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>KHM</t>
+  </si>
+  <si>
+    <t>Schengen</t>
+  </si>
+  <si>
+    <t>Frontex</t>
+  </si>
+  <si>
+    <t>circulation</t>
+  </si>
+  <si>
+    <t>drame</t>
+  </si>
+  <si>
+    <t>injustice</t>
+  </si>
+  <si>
+    <t>Afrique saharique</t>
+  </si>
+  <si>
+    <t>Arabie</t>
+  </si>
+  <si>
+    <t>STA_NAM_CHN</t>
+  </si>
+  <si>
+    <t>Japon</t>
+  </si>
+  <si>
+    <t>raphaelmasse5@gmail.com</t>
+  </si>
+  <si>
+    <t>942bff33-91f2-46eb-9785-1ad462daef7a</t>
+  </si>
+  <si>
+    <t>uuid:942bff33-91f2-46eb-9785-1ad462daef7a</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>JAM</t>
+  </si>
+  <si>
+    <t>Catholique</t>
+  </si>
+  <si>
+    <t>LTU</t>
+  </si>
+  <si>
+    <t>ancienneté</t>
+  </si>
+  <si>
+    <t>niveau de vie ++</t>
+  </si>
+  <si>
+    <t>géopolitique</t>
+  </si>
+  <si>
+    <t>nouveau continent</t>
+  </si>
+  <si>
+    <t>lieu de rencontre</t>
+  </si>
+  <si>
+    <t>mondialisation</t>
+  </si>
+  <si>
+    <t>expérience, vacance</t>
+  </si>
+  <si>
+    <t>Caraïbe le kiff</t>
+  </si>
+  <si>
+    <t>J'aime bien</t>
+  </si>
+  <si>
+    <t>bon pays pour le travail</t>
+  </si>
+  <si>
+    <t>pas bon pour le tourisme</t>
+  </si>
+  <si>
+    <t>ex-URSS</t>
+  </si>
+  <si>
+    <t>Usine textile</t>
+  </si>
+  <si>
+    <t>STA_NAM_IND</t>
+  </si>
+  <si>
+    <t>Chine + aire d'influence</t>
+  </si>
+  <si>
+    <t>domination mondiale</t>
+  </si>
+  <si>
+    <t>zacharieelin@gmail.com</t>
+  </si>
+  <si>
+    <t>3d3e6bfa-477b-4e6d-a132-34f834479198</t>
+  </si>
+  <si>
+    <t>uuid:300b3d41-833a-43ca-861e-990b64a466e8</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>OTAN</t>
+  </si>
+  <si>
+    <t>plage, vacances</t>
+  </si>
+  <si>
+    <t>Ricard</t>
+  </si>
+  <si>
+    <t>flux maritime</t>
+  </si>
+  <si>
+    <t>Pays des Nords</t>
+  </si>
+  <si>
+    <t>Puissance asiatique</t>
+  </si>
+  <si>
+    <t>Asie du Sud /Sud-Est</t>
+  </si>
+  <si>
+    <t>Moyen / Proche Orient</t>
+  </si>
+  <si>
+    <t>Amérique centrale / Sud</t>
+  </si>
+  <si>
+    <t>Australie / Nouvelle Zélande</t>
+  </si>
+  <si>
+    <t>charles.virlouvet2@gmail.com</t>
+  </si>
+  <si>
+    <t>00bc3394-6033-4a10-aa71-20636156d53c</t>
+  </si>
+  <si>
+    <t>uuid:00bc3394-6033-4a10-aa71-20636156d53c</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>vie</t>
+  </si>
+  <si>
+    <t>proximité</t>
+  </si>
+  <si>
+    <t>retraite</t>
+  </si>
+  <si>
+    <t>REG_ORG_ASI_Asean</t>
+  </si>
+  <si>
+    <t>Asie du Nord-Est</t>
+  </si>
+  <si>
+    <t>péninsule arabe</t>
+  </si>
+  <si>
+    <t>b652e990-a6fe-469e-90fa-be40b9fe7cd2</t>
+  </si>
+  <si>
+    <t>uuid:b652e990-a6fe-469e-90fa-be40b9fe7cd2</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>dispute</t>
+  </si>
+  <si>
+    <t>réfugiés</t>
+  </si>
+  <si>
+    <t>liaison</t>
+  </si>
+  <si>
+    <t>les "stans"</t>
+  </si>
+  <si>
+    <t>7948b4e9-cb27-4018-92df-404fa0698422</t>
+  </si>
+  <si>
+    <t>uuid:7948b4e9-cb27-4018-92df-404fa0698422</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
     <t>023</t>
-  </si>
-  <si>
-    <t>N1 N2 N3 N4 N5</t>
-  </si>
-  <si>
-    <t>monnaie commune</t>
-  </si>
-  <si>
-    <t>union européenne</t>
-  </si>
-  <si>
-    <t>centre</t>
-  </si>
-  <si>
-    <t>occident</t>
-  </si>
-  <si>
-    <t>littoral</t>
-  </si>
-  <si>
-    <t>pays du sud</t>
-  </si>
-  <si>
-    <t>équateur</t>
-  </si>
-  <si>
-    <t>REG_CON_EUR_centr</t>
-  </si>
-  <si>
-    <t>ef9f8d7a-dee1-4f84-b7e0-292d51cc4d9c</t>
-  </si>
-  <si>
-    <t>uuid:ef9f8d7a-dee1-4f84-b7e0-292d51cc4d9c</t>
-  </si>
-  <si>
-    <t>ara</t>
-  </si>
-  <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>OMN</t>
-  </si>
-  <si>
-    <t>UKR</t>
-  </si>
-  <si>
-    <t>COD</t>
-  </si>
-  <si>
-    <t>Nord</t>
-  </si>
-  <si>
-    <t>domination</t>
-  </si>
-  <si>
-    <t>pouvoir</t>
-  </si>
-  <si>
-    <t>olive</t>
-  </si>
-  <si>
-    <t>joie</t>
-  </si>
-  <si>
-    <t>histoire</t>
-  </si>
-  <si>
-    <t>mémoire</t>
-  </si>
-  <si>
-    <t>REG_CON_EUR_south</t>
-  </si>
-  <si>
-    <t>pays slaves</t>
-  </si>
-  <si>
-    <t>pays desi (?)</t>
-  </si>
-  <si>
-    <t>illisible</t>
-  </si>
-  <si>
-    <t>654e1025-e902-4382-b13a-67b4d02784da</t>
-  </si>
-  <si>
-    <t>uuid:654e1025-e902-4382-b13a-67b4d02784da</t>
-  </si>
-  <si>
-    <t>025</t>
-  </si>
-  <si>
-    <t>FIN</t>
-  </si>
-  <si>
-    <t>MTQ</t>
-  </si>
-  <si>
-    <t>froid</t>
-  </si>
-  <si>
-    <t>colonisateur</t>
-  </si>
-  <si>
-    <t>REG_CON_EUR_north</t>
-  </si>
-  <si>
-    <t>8f54acc8-a6d4-47ff-b972-8b3ad55e3fd7</t>
-  </si>
-  <si>
-    <t>uuid:8f54acc8-a6d4-47ff-b972-8b3ad55e3fd7</t>
-  </si>
-  <si>
-    <t>026</t>
-  </si>
-  <si>
-    <t>construction</t>
-  </si>
-  <si>
-    <t>eurocentrisme</t>
-  </si>
-  <si>
-    <t>antiquité héritage</t>
-  </si>
-  <si>
-    <t>interface</t>
-  </si>
-  <si>
-    <t>médiatisation</t>
-  </si>
-  <si>
-    <t>penseurs, hommes de lettre, négritude</t>
-  </si>
-  <si>
-    <t>Europe du Nord + Groeënland</t>
-  </si>
-  <si>
-    <t>Moyen et extrême Orient</t>
-  </si>
-  <si>
-    <t>Russie et une partie de l'Asie centrale</t>
-  </si>
-  <si>
-    <t>Asie du Sud / Inde</t>
-  </si>
-  <si>
-    <t>76690887-afb7-4c87-bb58-8a008a9d68b8</t>
-  </si>
-  <si>
-    <t>uuid:76690887-afb7-4c87-bb58-8a008a9d68b8</t>
-  </si>
-  <si>
-    <t>027</t>
-  </si>
-  <si>
-    <t>CMR</t>
-  </si>
-  <si>
-    <t>UZB</t>
-  </si>
-  <si>
-    <t>extrêmes droites</t>
-  </si>
-  <si>
-    <t>mauvais temps</t>
-  </si>
-  <si>
-    <t>multiculturelle</t>
-  </si>
-  <si>
-    <t>migrants</t>
-  </si>
-  <si>
-    <t>ressources naturelles</t>
-  </si>
-  <si>
-    <t>Moyen / Extrême Orient</t>
-  </si>
-  <si>
-    <t>hotlia3@gmail.com</t>
-  </si>
-  <si>
-    <t>c74041e0-3dc3-41a5-aff0-e43f82c35c76</t>
-  </si>
-  <si>
-    <t>uuid:c74041e0-3dc3-41a5-aff0-e43f82c35c76</t>
-  </si>
-  <si>
-    <t>028</t>
-  </si>
-  <si>
-    <t>fon</t>
-  </si>
-  <si>
-    <t>BFA</t>
-  </si>
-  <si>
-    <t>GHA</t>
-  </si>
-  <si>
-    <t>N1 N3 N4</t>
-  </si>
-  <si>
-    <t>KWT</t>
-  </si>
-  <si>
-    <t>SOM</t>
-  </si>
-  <si>
-    <t>continent européen</t>
-  </si>
-  <si>
-    <t>région européenne</t>
-  </si>
-  <si>
-    <t>espace schengen</t>
-  </si>
-  <si>
-    <t>climat méditerranéen</t>
-  </si>
-  <si>
-    <t>route commercial</t>
-  </si>
-  <si>
-    <t>flux</t>
-  </si>
-  <si>
-    <t>continent africain</t>
-  </si>
-  <si>
-    <t>Sahara</t>
-  </si>
-  <si>
-    <t>972d65de-832f-4327-9c8c-d97031e76a38</t>
-  </si>
-  <si>
-    <t>uuid:972d65de-832f-4327-9c8c-d97031e76a38</t>
-  </si>
-  <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>N1 N2 N3 N4</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>colonie</t>
-  </si>
-  <si>
-    <t>puissance historique</t>
-  </si>
-  <si>
-    <t>vaste</t>
-  </si>
-  <si>
-    <t>diversité frontalière</t>
-  </si>
-  <si>
-    <t>beau</t>
-  </si>
-  <si>
-    <t>a9b7212d-f30d-4b04-af69-60537ff38567</t>
-  </si>
-  <si>
-    <t>uuid:a9b7212d-f30d-4b04-af69-60537ff38567</t>
-  </si>
-  <si>
-    <t>030</t>
-  </si>
-  <si>
-    <t>xxx</t>
-  </si>
-  <si>
-    <t>MDV</t>
-  </si>
-  <si>
-    <t>NER</t>
-  </si>
-  <si>
-    <t>Espagne</t>
-  </si>
-  <si>
-    <t>Italie</t>
-  </si>
-  <si>
-    <t>Belgique</t>
-  </si>
-  <si>
-    <t>Allemagne</t>
-  </si>
-  <si>
-    <t>Afrique du Sud</t>
-  </si>
-  <si>
-    <t>Nigéria</t>
-  </si>
-  <si>
-    <t>Mali</t>
-  </si>
-  <si>
-    <t>Egypte</t>
-  </si>
-  <si>
-    <t>0df6765d-b313-4f73-bbcd-50111d64c4de</t>
-  </si>
-  <si>
-    <t>uuid:0df6765d-b313-4f73-bbcd-50111d64c4de</t>
-  </si>
-  <si>
-    <t>031</t>
-  </si>
-  <si>
-    <t>HTI</t>
-  </si>
-  <si>
-    <t>POL</t>
-  </si>
-  <si>
-    <t>faible</t>
-  </si>
-  <si>
-    <t>utopie</t>
-  </si>
-  <si>
-    <t>narcotraffic</t>
-  </si>
-  <si>
-    <t>potentiel</t>
-  </si>
-  <si>
-    <t>dictateurs</t>
-  </si>
-  <si>
-    <t>guerre / conflits</t>
-  </si>
-  <si>
-    <t>guerres éternelles</t>
-  </si>
-  <si>
-    <t>puissances orientales</t>
-  </si>
-  <si>
-    <t>bloc de l'humaisme</t>
-  </si>
-  <si>
-    <t>démocratie 155 mm</t>
-  </si>
-  <si>
-    <t>Drigs and Soy</t>
-  </si>
-  <si>
-    <t>scooters and t-shirts</t>
-  </si>
-  <si>
-    <t>the great COAL reef.</t>
-  </si>
-  <si>
-    <t>"chez eux"</t>
-  </si>
-  <si>
-    <t>ping pong</t>
-  </si>
-  <si>
-    <t>racists</t>
-  </si>
-  <si>
-    <t>they exists</t>
-  </si>
-  <si>
-    <t>AK-47, CIA, Wonderland</t>
-  </si>
-  <si>
-    <t>42947143-a948-49a7-bdcc-94cd8dc91286</t>
-  </si>
-  <si>
-    <t>uuid:42947143-a948-49a7-bdcc-94cd8dc91286</t>
-  </si>
-  <si>
-    <t>SMA-GR4</t>
-  </si>
-  <si>
-    <t>032</t>
-  </si>
-  <si>
-    <t>LIE</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>N1 N2 X</t>
-  </si>
-  <si>
-    <t>la région à côté</t>
-  </si>
-  <si>
-    <t>AND</t>
-  </si>
-  <si>
-    <t>Liechtenstein</t>
-  </si>
-  <si>
-    <t>continent</t>
-  </si>
-  <si>
-    <t>démocrates</t>
-  </si>
-  <si>
-    <t>Erasmus</t>
-  </si>
-  <si>
-    <t>plats</t>
-  </si>
-  <si>
-    <t>pêche</t>
-  </si>
-  <si>
-    <t>au milieu des terres</t>
-  </si>
-  <si>
-    <t>Bafoussam</t>
-  </si>
-  <si>
-    <t>Mafé</t>
-  </si>
-  <si>
-    <t>sol rouge</t>
-  </si>
-  <si>
-    <t>Afrique du Sud et de l'Est</t>
-  </si>
-  <si>
-    <t>tony77130@gmail.com</t>
-  </si>
-  <si>
-    <t>38fbb04c-f86d-4866-a34d-a9380c464d3a</t>
-  </si>
-  <si>
-    <t>uuid:38fbb04c-f86d-4866-a34d-a9380c464d3a</t>
-  </si>
-  <si>
-    <t>033</t>
-  </si>
-  <si>
-    <t>SVN</t>
-  </si>
-  <si>
-    <t>château</t>
-  </si>
-  <si>
-    <t>liberté</t>
-  </si>
-  <si>
-    <t>empire romain</t>
-  </si>
-  <si>
-    <t>Grèce antique</t>
-  </si>
-  <si>
-    <t>pyramide</t>
-  </si>
-  <si>
-    <t>famine</t>
-  </si>
-  <si>
-    <t>dictature</t>
-  </si>
-  <si>
-    <t>Québec libre</t>
-  </si>
-  <si>
-    <t>REG_CON_ASI_pacif</t>
-  </si>
-  <si>
-    <t>ed4fe0e2-e42f-4f10-a424-631105521e9f</t>
-  </si>
-  <si>
-    <t>uuid:ed4fe0e2-e42f-4f10-a424-631105521e9f</t>
-  </si>
-  <si>
-    <t>034</t>
-  </si>
-  <si>
-    <t>N1 N3</t>
-  </si>
-  <si>
-    <t>COL</t>
-  </si>
-  <si>
-    <t>blanc</t>
-  </si>
-  <si>
-    <t>stable</t>
-  </si>
-  <si>
-    <t>puissance</t>
-  </si>
-  <si>
-    <t>jeune</t>
-  </si>
-  <si>
-    <t>noire</t>
-  </si>
-  <si>
-    <t>ressource</t>
-  </si>
-  <si>
-    <t>conflit , vaste</t>
-  </si>
-  <si>
-    <t>REG_CON_EUR_south_east</t>
-  </si>
-  <si>
-    <t>pierrealexisgavrilenko@gmail.com</t>
-  </si>
-  <si>
-    <t>a8e2bebb-fd37-49ac-8652-dfdfd3fb4464</t>
-  </si>
-  <si>
-    <t>uuid:a17c93f4-35c3-4830-9a30-279353c5f329</t>
-  </si>
-  <si>
-    <t>035</t>
-  </si>
-  <si>
-    <t>LBN</t>
-  </si>
-  <si>
-    <t>lois</t>
-  </si>
-  <si>
-    <t>titre de séjour</t>
-  </si>
-  <si>
-    <t>eau</t>
-  </si>
-  <si>
-    <t>sous-développement</t>
-  </si>
-  <si>
-    <t>REG_CON_AMR</t>
-  </si>
-  <si>
-    <t>6b2e2e52-9566-414a-b94f-7eaf58fde5c9</t>
-  </si>
-  <si>
-    <t>uuid:6b2e2e52-9566-414a-b94f-7eaf58fde5c9</t>
-  </si>
-  <si>
-    <t>036</t>
-  </si>
-  <si>
-    <t>ARM</t>
-  </si>
-  <si>
-    <t>ROM</t>
-  </si>
-  <si>
-    <t>N1 N3 X</t>
-  </si>
-  <si>
-    <t>Yerevan</t>
-  </si>
-  <si>
-    <t>AZE</t>
-  </si>
-  <si>
-    <t>force, puissance</t>
-  </si>
-  <si>
-    <t>économie</t>
-  </si>
-  <si>
-    <t>traversée</t>
-  </si>
-  <si>
-    <t>dangers</t>
-  </si>
-  <si>
-    <t>côte</t>
-  </si>
-  <si>
-    <t>dictature militaire</t>
-  </si>
-  <si>
-    <t>tribus</t>
-  </si>
-  <si>
-    <t>Caucase / Proche-Orient</t>
-  </si>
-  <si>
-    <t>lois.petrossian@gmail.com</t>
-  </si>
-  <si>
-    <t>Plutôt que les paus de naissance, demander les origines.</t>
-  </si>
-  <si>
-    <t>182b1f2c-dcc8-4ca0-a7e2-05a2d54ed9f7</t>
-  </si>
-  <si>
-    <t>uuid:182b1f2c-dcc8-4ca0-a7e2-05a2d54ed9f7</t>
-  </si>
-  <si>
-    <t>037</t>
-  </si>
-  <si>
-    <t>N1 N2 N3 N4 N5 X</t>
-  </si>
-  <si>
-    <t>Cameroun-France métissage</t>
-  </si>
-  <si>
-    <t>chute démographique</t>
-  </si>
-  <si>
-    <t>centre du monde</t>
-  </si>
-  <si>
-    <t>pillage, occident</t>
-  </si>
-  <si>
-    <t>guerres</t>
-  </si>
-  <si>
-    <t>histoire (de sa région)</t>
-  </si>
-  <si>
-    <t>réchauffement climatique</t>
-  </si>
-  <si>
-    <t>ressources premières</t>
-  </si>
-  <si>
-    <t>espoir</t>
-  </si>
-  <si>
-    <t>héritages, conflits</t>
-  </si>
-  <si>
-    <t>Afrique "noire"</t>
-  </si>
-  <si>
-    <t>Océanie du sud</t>
-  </si>
-  <si>
-    <t>Océanie occidentale</t>
-  </si>
-  <si>
-    <t>Russie ? ni Europe, ni Asie, en guerre</t>
-  </si>
-  <si>
-    <t>2def15b5-17ac-4362-97e8-1b19437722ca</t>
-  </si>
-  <si>
-    <t>uuid:2def15b5-17ac-4362-97e8-1b19437722ca</t>
-  </si>
-  <si>
-    <t>038</t>
-  </si>
-  <si>
-    <t>guerre historique</t>
-  </si>
-  <si>
-    <t>culture culinaire</t>
-  </si>
-  <si>
-    <t>défis futus</t>
-  </si>
-  <si>
-    <t>chaud</t>
-  </si>
-  <si>
-    <t>savane</t>
-  </si>
-  <si>
-    <t>art tribal</t>
-  </si>
-  <si>
-    <t>empire colonial</t>
-  </si>
-  <si>
-    <t>richesse culturelle</t>
-  </si>
-  <si>
-    <t>Le Monde</t>
-  </si>
-  <si>
-    <t>3dfc76e2-647b-42df-938d-520bff479dac</t>
-  </si>
-  <si>
-    <t>uuid:3dfc76e2-647b-42df-938d-520bff479dac</t>
-  </si>
-  <si>
-    <t>039</t>
-  </si>
-  <si>
-    <t>N2 N3 N4</t>
-  </si>
-  <si>
-    <t>perte de vitesse</t>
-  </si>
-  <si>
-    <t>identité</t>
-  </si>
-  <si>
-    <t>vanité</t>
-  </si>
-  <si>
-    <t>défi</t>
-  </si>
-  <si>
-    <t>inondation</t>
-  </si>
-  <si>
-    <t>hurricane</t>
-  </si>
-  <si>
-    <t>bleue</t>
-  </si>
-  <si>
-    <t>tradition</t>
-  </si>
-  <si>
-    <t>avenir</t>
-  </si>
-  <si>
-    <t>lion</t>
-  </si>
-  <si>
-    <t>Monde</t>
-  </si>
-  <si>
-    <t>96f48454-85e4-4b46-8a00-b3afcd3359f7</t>
-  </si>
-  <si>
-    <t>uuid:96f48454-85e4-4b46-8a00-b3afcd3359f7</t>
-  </si>
-  <si>
-    <t>040</t>
-  </si>
-  <si>
-    <t>NPL</t>
-  </si>
-  <si>
-    <t>unité</t>
-  </si>
-  <si>
-    <t>projet</t>
-  </si>
-  <si>
-    <t>défis</t>
-  </si>
-  <si>
-    <t>mare nostrum</t>
-  </si>
-  <si>
-    <t>cuisine</t>
-  </si>
-  <si>
-    <t>tristesse</t>
-  </si>
-  <si>
-    <t>inconnu</t>
-  </si>
-  <si>
-    <t>zone tropicale</t>
-  </si>
-  <si>
-    <t>zone subtropicale</t>
-  </si>
-  <si>
-    <t>zone tempérée</t>
-  </si>
-  <si>
-    <t>zone polaire / subpolaire</t>
-  </si>
-  <si>
-    <t>ca71aaa8-369d-4896-a2ad-7221e9826990</t>
-  </si>
-  <si>
-    <t>uuid:ca71aaa8-369d-4896-a2ad-7221e9826990</t>
-  </si>
-  <si>
-    <t>041</t>
-  </si>
-  <si>
-    <t>voyage</t>
-  </si>
-  <si>
-    <t>un petit dauphin</t>
-  </si>
-  <si>
-    <t>centralité</t>
-  </si>
-  <si>
-    <t>en développement</t>
-  </si>
-  <si>
-    <t>faune</t>
-  </si>
-  <si>
-    <t>natures</t>
-  </si>
-  <si>
-    <t>56a2b4a5-4d39-4ce2-abd2-66eea92431eb</t>
-  </si>
-  <si>
-    <t>uuid:56a2b4a5-4d39-4ce2-abd2-66eea92431eb</t>
-  </si>
-  <si>
-    <t>042</t>
-  </si>
-  <si>
-    <t>température de l'eau</t>
-  </si>
-  <si>
-    <t>beaucoup de monde</t>
-  </si>
-  <si>
-    <t>sourire</t>
-  </si>
-  <si>
-    <t>sécheresse</t>
-  </si>
-  <si>
-    <t>safaris, diversité, animaux, paysages, beauté</t>
-  </si>
-  <si>
-    <t>976c8ea7-30e4-4af9-b171-61503887bb24</t>
-  </si>
-  <si>
-    <t>uuid:976c8ea7-30e4-4af9-b171-61503887bb24</t>
-  </si>
-  <si>
-    <t>043</t>
-  </si>
-  <si>
-    <t>GTM</t>
-  </si>
-  <si>
-    <t>guerre froide</t>
-  </si>
-  <si>
-    <t>royaume</t>
-  </si>
-  <si>
-    <t>soft power</t>
-  </si>
-  <si>
-    <t>Gibraltar</t>
-  </si>
-  <si>
-    <t>population</t>
-  </si>
-  <si>
-    <t>préhistoire</t>
-  </si>
-  <si>
-    <t>sahara</t>
-  </si>
-  <si>
-    <t>408f7c1f-5da5-4a59-a1de-3bee328ee2d4</t>
-  </si>
-  <si>
-    <t>uuid:408f7c1f-5da5-4a59-a1de-3bee328ee2d4</t>
-  </si>
-  <si>
-    <t>044</t>
-  </si>
-  <si>
-    <t>chancceux</t>
-  </si>
-  <si>
-    <t>cohésion</t>
-  </si>
-  <si>
-    <t>rainistification (?)</t>
-  </si>
-  <si>
-    <t>nature</t>
-  </si>
-  <si>
-    <t>beauté</t>
-  </si>
-  <si>
-    <t>980e233c-9d91-45f3-be71-1ced246c1126</t>
-  </si>
-  <si>
-    <t>uuid:980e233c-9d91-45f3-be71-1ced246c1126</t>
-  </si>
-  <si>
-    <t>045</t>
-  </si>
-  <si>
-    <t>voyages</t>
-  </si>
-  <si>
-    <t>villes</t>
-  </si>
-  <si>
-    <t>pollution</t>
-  </si>
-  <si>
-    <t>surconsommation</t>
-  </si>
-  <si>
-    <t>ports</t>
-  </si>
-  <si>
-    <t>animaux</t>
-  </si>
-  <si>
-    <t>8650fa0e-8d2a-40b8-999d-73b93bd18099</t>
-  </si>
-  <si>
-    <t>uuid:8650fa0e-8d2a-40b8-999d-73b93bd18099</t>
-  </si>
-  <si>
-    <t>046</t>
-  </si>
-  <si>
-    <t>TCD</t>
-  </si>
-  <si>
-    <t>travail</t>
-  </si>
-  <si>
-    <t>plages</t>
-  </si>
-  <si>
-    <t>nature, forêts</t>
-  </si>
-  <si>
-    <t>f6a68bc5-8ac9-4350-9f40-45c553ae5977</t>
-  </si>
-  <si>
-    <t>uuid:f6a68bc5-8ac9-4350-9f40-45c553ae5977</t>
-  </si>
-  <si>
-    <t>047</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
-    <t>MKD</t>
-  </si>
-  <si>
-    <t>KOS</t>
-  </si>
-  <si>
-    <t>SRB</t>
-  </si>
-  <si>
-    <t>Nords</t>
-  </si>
-  <si>
-    <t>séparation</t>
-  </si>
-  <si>
-    <t>tragédie</t>
-  </si>
-  <si>
-    <t>futur</t>
-  </si>
-  <si>
-    <t>investissement</t>
-  </si>
-  <si>
-    <t>REG_OTH_SEA_atlantic</t>
-  </si>
-  <si>
-    <t>lepape.nils@gmail.com</t>
-  </si>
-  <si>
-    <t>13383b26-6917-4309-912c-7c45922fef3c</t>
-  </si>
-  <si>
-    <t>uuid:13383b26-6917-4309-912c-7c45922fef3c</t>
-  </si>
-  <si>
-    <t>048</t>
-  </si>
-  <si>
-    <t>srp</t>
-  </si>
-  <si>
-    <t>religion</t>
-  </si>
-  <si>
-    <t>montagne</t>
-  </si>
-  <si>
-    <t>châteaux</t>
-  </si>
-  <si>
-    <t>football</t>
-  </si>
-  <si>
-    <t>entraide</t>
-  </si>
-  <si>
-    <t>calme</t>
-  </si>
-  <si>
-    <t>beauté, paysage</t>
-  </si>
-  <si>
-    <t>fruits, nourriture fraîche</t>
-  </si>
-  <si>
-    <t>diversité, paysage</t>
-  </si>
-  <si>
-    <t>exotisme</t>
-  </si>
-  <si>
-    <t>Nord riche</t>
-  </si>
-  <si>
-    <t>Océan</t>
-  </si>
-  <si>
-    <t>Asie Sud / Océanie</t>
-  </si>
-  <si>
-    <t>147776f8-ff9c-4149-951b-703dd52342f9</t>
-  </si>
-  <si>
-    <t>uuid:774d985b-af79-4ca3-9d82-d32ce8244293</t>
-  </si>
-  <si>
-    <t>SMA-GR3</t>
-  </si>
-  <si>
-    <t>049</t>
-  </si>
-  <si>
-    <t>DOM</t>
-  </si>
-  <si>
-    <t>IDN</t>
-  </si>
-  <si>
-    <t>monnaie</t>
-  </si>
-  <si>
-    <t>agriculture</t>
-  </si>
-  <si>
-    <t>divers</t>
-  </si>
-  <si>
-    <t>pauvre</t>
-  </si>
-  <si>
-    <t>pillée</t>
-  </si>
-  <si>
-    <t>STA_NAM_USA</t>
-  </si>
-  <si>
-    <t>démocarties des Nords</t>
-  </si>
-  <si>
-    <t>justinbarrault7@gmail.com</t>
-  </si>
-  <si>
-    <t>a777d387-c97b-4e49-bb5e-51874fba3956</t>
-  </si>
-  <si>
-    <t>uuid:bba89295-293e-4ef5-8b5c-2ff00def4f2e</t>
-  </si>
-  <si>
-    <t>050</t>
-  </si>
-  <si>
-    <t>espace Schengen</t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t>salade</t>
-  </si>
-  <si>
-    <t>Côte d'azur</t>
-  </si>
-  <si>
-    <t>foutou</t>
-  </si>
-  <si>
-    <t>Maghreb</t>
-  </si>
-  <si>
-    <t>Amérique des "Nords"</t>
-  </si>
-  <si>
-    <t>STA_NAM_BRA</t>
-  </si>
-  <si>
-    <t>Europe de l'Est / Moyen Orient</t>
-  </si>
-  <si>
-    <t>puichaffretjoseph@gmail.com</t>
-  </si>
-  <si>
-    <t>8d6b2038-cb8d-4719-941d-8a5a963e56e4</t>
-  </si>
-  <si>
-    <t>uuid:8d6b2038-cb8d-4719-941d-8a5a963e56e4</t>
-  </si>
-  <si>
-    <t>051</t>
-  </si>
-  <si>
-    <t>urd</t>
-  </si>
-  <si>
-    <t>été, vacances</t>
-  </si>
-  <si>
-    <t>morts, noyades</t>
-  </si>
-  <si>
-    <t>inégalitaire</t>
-  </si>
-  <si>
-    <t>très très diverse</t>
-  </si>
-  <si>
-    <t>prospérité</t>
-  </si>
-  <si>
-    <t>colonies</t>
-  </si>
-  <si>
-    <t>557ec1d0-c074-4288-99d9-f9b2656edbf5</t>
-  </si>
-  <si>
-    <t>uuid:a2540619-c477-4d84-88a3-eb3bf4c5d7fe</t>
-  </si>
-  <si>
-    <t>052</t>
-  </si>
-  <si>
-    <t>TWN</t>
-  </si>
-  <si>
-    <t>Pays riches</t>
-  </si>
-  <si>
-    <t>Europe / Afrique / Asie</t>
-  </si>
-  <si>
-    <t>Sud</t>
-  </si>
-  <si>
-    <t>néocolonialisme</t>
-  </si>
-  <si>
-    <t>REG_CON_ASI_north</t>
-  </si>
-  <si>
-    <t>3d6eae70-bff9-41a4-8386-f8b5e03ecbb0</t>
-  </si>
-  <si>
-    <t>uuid:3d6eae70-bff9-41a4-8386-f8b5e03ecbb0</t>
-  </si>
-  <si>
-    <t>053</t>
-  </si>
-  <si>
-    <t>wol</t>
-  </si>
-  <si>
-    <t>ita</t>
-  </si>
-  <si>
-    <t>pays musulmans</t>
-  </si>
-  <si>
-    <t>Grèce</t>
-  </si>
-  <si>
-    <t>Cameroun</t>
-  </si>
-  <si>
-    <t>Maroc</t>
-  </si>
-  <si>
-    <t>Côte d'Ivoire</t>
-  </si>
-  <si>
-    <t>penda.mbaye136@gmail.com</t>
-  </si>
-  <si>
-    <t>46026cae-c90e-4c99-8970-9b116346d617</t>
-  </si>
-  <si>
-    <t>uuid:46026cae-c90e-4c99-8970-9b116346d617</t>
-  </si>
-  <si>
-    <t>054</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>maison</t>
-  </si>
-  <si>
-    <t>enjeux</t>
-  </si>
-  <si>
-    <t>abondance</t>
-  </si>
-  <si>
-    <t>huile</t>
-  </si>
-  <si>
-    <t>Barcelonne</t>
-  </si>
-  <si>
-    <t>forêt tropicale</t>
-  </si>
-  <si>
-    <t>inégalités</t>
-  </si>
-  <si>
-    <t>pôle Nord</t>
-  </si>
-  <si>
-    <t>48f69873-75b5-4e98-812f-3cac6d012f4b</t>
-  </si>
-  <si>
-    <t>uuid:48f69873-75b5-4e98-812f-3cac6d012f4b</t>
-  </si>
-  <si>
-    <t>055</t>
-  </si>
-  <si>
-    <t>ancien</t>
-  </si>
-  <si>
-    <t>vigne</t>
-  </si>
-  <si>
-    <t>colonisé</t>
-  </si>
-  <si>
-    <t>Asie peuplée</t>
-  </si>
-  <si>
-    <t>8bdeea2d-310d-4c7e-b67f-cad9e70738f3</t>
-  </si>
-  <si>
-    <t>uuid:8bdeea2d-310d-4c7e-b67f-cad9e70738f3</t>
-  </si>
-  <si>
-    <t>056</t>
-  </si>
-  <si>
-    <t>NIC</t>
-  </si>
-  <si>
-    <t>PAN</t>
-  </si>
-  <si>
-    <t>déclin</t>
-  </si>
-  <si>
-    <t>fascisme</t>
-  </si>
-  <si>
-    <t>Sicile</t>
-  </si>
-  <si>
-    <t>berceau</t>
-  </si>
-  <si>
-    <t>esclavage</t>
-  </si>
-  <si>
-    <t>exploité</t>
-  </si>
-  <si>
-    <t>Les Nords</t>
-  </si>
-  <si>
-    <t>Les Suds</t>
-  </si>
-  <si>
-    <t>c2557764-e156-4dd2-afd2-fe1ed0325c34</t>
-  </si>
-  <si>
-    <t>uuid:c2557764-e156-4dd2-afd2-fe1ed0325c34</t>
-  </si>
-  <si>
-    <t>057</t>
-  </si>
-  <si>
-    <t>KHM</t>
-  </si>
-  <si>
-    <t>Schengen</t>
-  </si>
-  <si>
-    <t>Frontex</t>
-  </si>
-  <si>
-    <t>circulation</t>
-  </si>
-  <si>
-    <t>drame</t>
-  </si>
-  <si>
-    <t>injustice</t>
-  </si>
-  <si>
-    <t>Afrique saharique</t>
-  </si>
-  <si>
-    <t>Arabie</t>
-  </si>
-  <si>
-    <t>STA_NAM_CHN</t>
-  </si>
-  <si>
-    <t>Japon</t>
-  </si>
-  <si>
-    <t>raphaelmasse5@gmail.com</t>
-  </si>
-  <si>
-    <t>942bff33-91f2-46eb-9785-1ad462daef7a</t>
-  </si>
-  <si>
-    <t>uuid:942bff33-91f2-46eb-9785-1ad462daef7a</t>
-  </si>
-  <si>
-    <t>058</t>
-  </si>
-  <si>
-    <t>JAM</t>
-  </si>
-  <si>
-    <t>Catholique</t>
-  </si>
-  <si>
-    <t>LTU</t>
-  </si>
-  <si>
-    <t>ancienneté</t>
-  </si>
-  <si>
-    <t>niveau de vie ++</t>
-  </si>
-  <si>
-    <t>géopolitique</t>
-  </si>
-  <si>
-    <t>nouveau continent</t>
-  </si>
-  <si>
-    <t>lieu de rencontre</t>
-  </si>
-  <si>
-    <t>mondialisation</t>
-  </si>
-  <si>
-    <t>expérience, vacance</t>
-  </si>
-  <si>
-    <t>Caraïbe le kiff</t>
-  </si>
-  <si>
-    <t>J'aime bien</t>
-  </si>
-  <si>
-    <t>bon pays pour le travail</t>
-  </si>
-  <si>
-    <t>pas bon pour le tourisme</t>
-  </si>
-  <si>
-    <t>ex-URSS</t>
-  </si>
-  <si>
-    <t>Usine textile</t>
-  </si>
-  <si>
-    <t>STA_NAM_IND</t>
-  </si>
-  <si>
-    <t>Chine + aire d'influence</t>
-  </si>
-  <si>
-    <t>domination mondiale</t>
-  </si>
-  <si>
-    <t>zacharieelin@gmail.com</t>
-  </si>
-  <si>
-    <t>3d3e6bfa-477b-4e6d-a132-34f834479198</t>
-  </si>
-  <si>
-    <t>uuid:300b3d41-833a-43ca-861e-990b64a466e8</t>
-  </si>
-  <si>
-    <t>059</t>
-  </si>
-  <si>
-    <t>OTAN</t>
-  </si>
-  <si>
-    <t>plage, vacances</t>
-  </si>
-  <si>
-    <t>Ricard</t>
-  </si>
-  <si>
-    <t>flux maritime</t>
-  </si>
-  <si>
-    <t>Pays des Nords</t>
-  </si>
-  <si>
-    <t>Puissance asiatique</t>
-  </si>
-  <si>
-    <t>Asie du Sud /Sud-Est</t>
-  </si>
-  <si>
-    <t>Moyen / Proche Orient</t>
-  </si>
-  <si>
-    <t>Amérique centrale / Sud</t>
-  </si>
-  <si>
-    <t>Australie / Nouvelle Zélande</t>
-  </si>
-  <si>
-    <t>charles.virlouvet2@gmail.com</t>
-  </si>
-  <si>
-    <t>00bc3394-6033-4a10-aa71-20636156d53c</t>
-  </si>
-  <si>
-    <t>uuid:00bc3394-6033-4a10-aa71-20636156d53c</t>
-  </si>
-  <si>
-    <t>060</t>
-  </si>
-  <si>
-    <t>vie</t>
-  </si>
-  <si>
-    <t>proximité</t>
-  </si>
-  <si>
-    <t>retraite</t>
-  </si>
-  <si>
-    <t>REG_ORG_ASI_Asean</t>
-  </si>
-  <si>
-    <t>Asie du Nord-Est</t>
-  </si>
-  <si>
-    <t>péninsule arabe</t>
-  </si>
-  <si>
-    <t>b652e990-a6fe-469e-90fa-be40b9fe7cd2</t>
-  </si>
-  <si>
-    <t>uuid:b652e990-a6fe-469e-90fa-be40b9fe7cd2</t>
-  </si>
-  <si>
-    <t>061</t>
-  </si>
-  <si>
-    <t>dispute</t>
-  </si>
-  <si>
-    <t>réfugiés</t>
-  </si>
-  <si>
-    <t>liaison</t>
-  </si>
-  <si>
-    <t>les "stans"</t>
-  </si>
-  <si>
-    <t>7948b4e9-cb27-4018-92df-404fa0698422</t>
-  </si>
-  <si>
-    <t>uuid:7948b4e9-cb27-4018-92df-404fa0698422</t>
   </si>
 </sst>
 </file>
@@ -4829,10 +4832,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4858,9 +4867,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12397,8 +12407,8 @@
       <c r="D24" t="s">
         <v>997</v>
       </c>
-      <c r="E24" t="s">
-        <v>1099</v>
+      <c r="E24" s="2" t="s">
+        <v>1600</v>
       </c>
       <c r="F24" s="1">
         <v>46104</v>
@@ -12464,7 +12474,7 @@
         <v>5</v>
       </c>
       <c r="AO24" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AP24">
         <v>1</v>
@@ -12506,19 +12516,19 @@
         <v>677</v>
       </c>
       <c r="BH24" t="s">
+        <v>1100</v>
+      </c>
+      <c r="BI24" t="s">
         <v>1101</v>
       </c>
-      <c r="BI24" t="s">
+      <c r="BJ24" t="s">
         <v>1102</v>
       </c>
-      <c r="BJ24" t="s">
+      <c r="BK24" t="s">
         <v>1103</v>
       </c>
-      <c r="BK24" t="s">
+      <c r="BM24" t="s">
         <v>1104</v>
-      </c>
-      <c r="BM24" t="s">
-        <v>1105</v>
       </c>
       <c r="BN24" t="s">
         <v>893</v>
@@ -12533,10 +12543,10 @@
         <v>942</v>
       </c>
       <c r="BS24" t="s">
+        <v>1105</v>
+      </c>
+      <c r="BT24" t="s">
         <v>1106</v>
-      </c>
-      <c r="BT24" t="s">
-        <v>1107</v>
       </c>
       <c r="BU24" t="s">
         <v>922</v>
@@ -12554,7 +12564,7 @@
         <v>776</v>
       </c>
       <c r="CG24" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="CI24" t="s">
         <v>707</v>
@@ -12581,7 +12591,7 @@
         <v>708698573</v>
       </c>
       <c r="YF24" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="YG24" s="1">
         <v>46108.485914351862</v>
@@ -12593,7 +12603,7 @@
         <v>1076</v>
       </c>
       <c r="YN24" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="YO24">
         <v>23</v>
@@ -12610,7 +12620,7 @@
         <v>997</v>
       </c>
       <c r="E25" t="s">
-        <v>1099</v>
+        <v>1599</v>
       </c>
       <c r="F25" s="1">
         <v>46104</v>
@@ -12649,16 +12659,16 @@
         <v>1062</v>
       </c>
       <c r="U25" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="X25" t="s">
         <v>1062</v>
       </c>
       <c r="Y25" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Z25" t="s">
         <v>1111</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>1112</v>
       </c>
       <c r="AB25" t="s">
         <v>671</v>
@@ -12715,7 +12725,7 @@
         <v>1002</v>
       </c>
       <c r="BA25" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="BB25" t="s">
         <v>806</v>
@@ -12727,13 +12737,13 @@
         <v>866</v>
       </c>
       <c r="BE25" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="BF25" t="s">
         <v>845</v>
       </c>
       <c r="BG25" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="BH25" t="s">
         <v>809</v>
@@ -12742,13 +12752,13 @@
         <v>687</v>
       </c>
       <c r="BJ25" t="s">
+        <v>1115</v>
+      </c>
+      <c r="BK25" t="s">
         <v>1116</v>
       </c>
-      <c r="BK25" t="s">
+      <c r="BL25" t="s">
         <v>1117</v>
-      </c>
-      <c r="BL25" t="s">
-        <v>1118</v>
       </c>
       <c r="BM25" t="s">
         <v>893</v>
@@ -12760,22 +12770,22 @@
         <v>915</v>
       </c>
       <c r="BP25" t="s">
+        <v>1118</v>
+      </c>
+      <c r="BQ25" t="s">
         <v>1119</v>
-      </c>
-      <c r="BQ25" t="s">
-        <v>1120</v>
       </c>
       <c r="BR25" t="s">
         <v>958</v>
       </c>
       <c r="BS25" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="BT25" t="s">
         <v>895</v>
       </c>
       <c r="BU25" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="BV25" t="s">
         <v>747</v>
@@ -12790,13 +12800,13 @@
         <v>944</v>
       </c>
       <c r="CG25" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="CI25" t="s">
         <v>705</v>
       </c>
       <c r="CJ25" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="CK25" t="s">
         <v>1093</v>
@@ -12820,7 +12830,7 @@
         <v>705</v>
       </c>
       <c r="CX25" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="CY25" t="s">
         <v>735</v>
@@ -12832,13 +12842,13 @@
         <v>671</v>
       </c>
       <c r="DN25" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="YE25">
         <v>708704343</v>
       </c>
       <c r="YF25" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="YG25" s="1">
         <v>46108.491180555553</v>
@@ -12850,7 +12860,7 @@
         <v>1076</v>
       </c>
       <c r="YN25" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="YO25">
         <v>24</v>
@@ -12867,7 +12877,7 @@
         <v>997</v>
       </c>
       <c r="E26" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F26" s="1">
         <v>46104</v>
@@ -12909,13 +12919,13 @@
         <v>1062</v>
       </c>
       <c r="U26" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="X26" t="s">
         <v>1062</v>
       </c>
       <c r="Y26" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="AB26" t="s">
         <v>736</v>
@@ -12936,7 +12946,7 @@
         <v>683</v>
       </c>
       <c r="AJ26" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="AK26">
         <v>5</v>
@@ -12978,7 +12988,7 @@
         <v>678</v>
       </c>
       <c r="AZ26" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="BA26" t="s">
         <v>1022</v>
@@ -13002,10 +13012,10 @@
         <v>687</v>
       </c>
       <c r="BI26" t="s">
+        <v>1131</v>
+      </c>
+      <c r="BJ26" t="s">
         <v>1132</v>
-      </c>
-      <c r="BJ26" t="s">
-        <v>1133</v>
       </c>
       <c r="BM26" t="s">
         <v>1087</v>
@@ -13038,7 +13048,7 @@
         <v>701</v>
       </c>
       <c r="CK26" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="CM26" t="s">
         <v>699</v>
@@ -13062,7 +13072,7 @@
         <v>708708442</v>
       </c>
       <c r="YF26" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="YG26" s="1">
         <v>46108.494791666657</v>
@@ -13074,7 +13084,7 @@
         <v>1076</v>
       </c>
       <c r="YN26" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="YO26">
         <v>25</v>
@@ -13091,7 +13101,7 @@
         <v>997</v>
       </c>
       <c r="E27" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="F27" s="1">
         <v>46104</v>
@@ -13205,13 +13215,13 @@
         <v>958</v>
       </c>
       <c r="BJ27" t="s">
+        <v>1137</v>
+      </c>
+      <c r="BK27" t="s">
+        <v>1103</v>
+      </c>
+      <c r="BL27" t="s">
         <v>1138</v>
-      </c>
-      <c r="BK27" t="s">
-        <v>1104</v>
-      </c>
-      <c r="BL27" t="s">
-        <v>1139</v>
       </c>
       <c r="BM27" t="s">
         <v>853</v>
@@ -13223,10 +13233,10 @@
         <v>852</v>
       </c>
       <c r="BP27" t="s">
+        <v>1139</v>
+      </c>
+      <c r="BQ27" t="s">
         <v>1140</v>
-      </c>
-      <c r="BQ27" t="s">
-        <v>1141</v>
       </c>
       <c r="BR27" t="s">
         <v>1068</v>
@@ -13238,10 +13248,10 @@
         <v>747</v>
       </c>
       <c r="BU27" t="s">
+        <v>1141</v>
+      </c>
+      <c r="BV27" t="s">
         <v>1142</v>
-      </c>
-      <c r="BV27" t="s">
-        <v>1143</v>
       </c>
       <c r="CA27" t="s">
         <v>702</v>
@@ -13259,7 +13269,7 @@
         <v>705</v>
       </c>
       <c r="CJ27" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="CK27" t="s">
         <v>753</v>
@@ -13277,19 +13287,19 @@
         <v>705</v>
       </c>
       <c r="CT27" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="CU27" t="s">
         <v>705</v>
       </c>
       <c r="CV27" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="CW27" t="s">
         <v>705</v>
       </c>
       <c r="CX27" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="CY27" t="s">
         <v>733</v>
@@ -13304,7 +13314,7 @@
         <v>708714509</v>
       </c>
       <c r="YF27" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="YG27" s="1">
         <v>46108.499560185177</v>
@@ -13316,7 +13326,7 @@
         <v>1076</v>
       </c>
       <c r="YN27" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="YO27">
         <v>26</v>
@@ -13333,7 +13343,7 @@
         <v>997</v>
       </c>
       <c r="E28" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="F28" s="1">
         <v>46104</v>
@@ -13363,7 +13373,7 @@
         <v>670</v>
       </c>
       <c r="Q28" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="R28" t="s">
         <v>670</v>
@@ -13387,7 +13397,7 @@
         <v>677</v>
       </c>
       <c r="AJ28" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="AK28">
         <v>5</v>
@@ -13444,13 +13454,13 @@
         <v>679</v>
       </c>
       <c r="BH28" t="s">
+        <v>1152</v>
+      </c>
+      <c r="BI28" t="s">
         <v>1153</v>
       </c>
-      <c r="BI28" t="s">
+      <c r="BJ28" t="s">
         <v>1154</v>
-      </c>
-      <c r="BJ28" t="s">
-        <v>1155</v>
       </c>
       <c r="BK28" t="s">
         <v>687</v>
@@ -13459,7 +13469,7 @@
         <v>747</v>
       </c>
       <c r="BM28" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="BN28" t="s">
         <v>915</v>
@@ -13471,7 +13481,7 @@
         <v>719</v>
       </c>
       <c r="BS28" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="BT28" t="s">
         <v>993</v>
@@ -13480,7 +13490,7 @@
         <v>939</v>
       </c>
       <c r="BV28" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="CA28" t="s">
         <v>702</v>
@@ -13513,7 +13523,7 @@
         <v>860</v>
       </c>
       <c r="CU28" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="CW28" t="s">
         <v>753</v>
@@ -13522,7 +13532,7 @@
         <v>705</v>
       </c>
       <c r="CZ28" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="DA28" t="s">
         <v>775</v>
@@ -13534,13 +13544,13 @@
         <v>671</v>
       </c>
       <c r="DN28" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="YE28">
         <v>708720006</v>
       </c>
       <c r="YF28" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="YG28" s="1">
         <v>46108.50372685185</v>
@@ -13552,7 +13562,7 @@
         <v>1076</v>
       </c>
       <c r="YN28" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="YO28">
         <v>27</v>
@@ -13569,7 +13579,7 @@
         <v>997</v>
       </c>
       <c r="E29" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="F29" s="1">
         <v>46104</v>
@@ -13605,7 +13615,7 @@
         <v>982</v>
       </c>
       <c r="T29" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="U29" t="s">
         <v>1062</v>
@@ -13623,10 +13633,10 @@
         <v>982</v>
       </c>
       <c r="AE29" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AF29" t="s">
         <v>1164</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>1165</v>
       </c>
       <c r="AG29" t="s">
         <v>678</v>
@@ -13644,7 +13654,7 @@
         <v>5</v>
       </c>
       <c r="AO29" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AP29">
         <v>1</v>
@@ -13689,43 +13699,43 @@
         <v>721</v>
       </c>
       <c r="BF29" t="s">
+        <v>1166</v>
+      </c>
+      <c r="BG29" t="s">
         <v>1167</v>
-      </c>
-      <c r="BG29" t="s">
-        <v>1168</v>
       </c>
       <c r="BH29" t="s">
         <v>809</v>
       </c>
       <c r="BI29" t="s">
+        <v>1168</v>
+      </c>
+      <c r="BJ29" t="s">
         <v>1169</v>
       </c>
-      <c r="BJ29" t="s">
+      <c r="BK29" t="s">
+        <v>1101</v>
+      </c>
+      <c r="BL29" t="s">
         <v>1170</v>
       </c>
-      <c r="BK29" t="s">
-        <v>1102</v>
-      </c>
-      <c r="BL29" t="s">
+      <c r="BM29" t="s">
         <v>1171</v>
-      </c>
-      <c r="BM29" t="s">
-        <v>1172</v>
       </c>
       <c r="BN29" t="s">
         <v>955</v>
       </c>
       <c r="BO29" t="s">
+        <v>1172</v>
+      </c>
+      <c r="BP29" t="s">
         <v>1173</v>
       </c>
-      <c r="BP29" t="s">
+      <c r="BR29" t="s">
         <v>1174</v>
       </c>
-      <c r="BR29" t="s">
+      <c r="BS29" t="s">
         <v>1175</v>
-      </c>
-      <c r="BS29" t="s">
-        <v>1176</v>
       </c>
       <c r="BT29" t="s">
         <v>747</v>
@@ -13761,7 +13771,7 @@
         <v>708766362</v>
       </c>
       <c r="YF29" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="YG29" s="1">
         <v>46108.535324074073</v>
@@ -13773,7 +13783,7 @@
         <v>1076</v>
       </c>
       <c r="YN29" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="YO29">
         <v>28</v>
@@ -13790,7 +13800,7 @@
         <v>997</v>
       </c>
       <c r="E30" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="F30" s="1">
         <v>46104</v>
@@ -13856,7 +13866,7 @@
         <v>7</v>
       </c>
       <c r="AO30" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AP30">
         <v>1</v>
@@ -13883,7 +13893,7 @@
         <v>1045</v>
       </c>
       <c r="AZ30" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="BA30" t="s">
         <v>843</v>
@@ -13895,7 +13905,7 @@
         <v>721</v>
       </c>
       <c r="BD30" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="BE30" t="s">
         <v>674</v>
@@ -13907,22 +13917,22 @@
         <v>1079</v>
       </c>
       <c r="BH30" t="s">
+        <v>1181</v>
+      </c>
+      <c r="BI30" t="s">
         <v>1182</v>
-      </c>
-      <c r="BI30" t="s">
-        <v>1183</v>
       </c>
       <c r="BM30" t="s">
         <v>936</v>
       </c>
       <c r="BN30" t="s">
+        <v>1183</v>
+      </c>
+      <c r="BO30" t="s">
         <v>1184</v>
       </c>
-      <c r="BO30" t="s">
+      <c r="BP30" t="s">
         <v>1185</v>
-      </c>
-      <c r="BP30" t="s">
-        <v>1186</v>
       </c>
       <c r="BR30" t="s">
         <v>942</v>
@@ -13970,7 +13980,7 @@
         <v>708772726</v>
       </c>
       <c r="YF30" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="YG30" s="1">
         <v>46108.539120370369</v>
@@ -13982,7 +13992,7 @@
         <v>1076</v>
       </c>
       <c r="YN30" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="YO30">
         <v>29</v>
@@ -13999,7 +14009,7 @@
         <v>997</v>
       </c>
       <c r="E31" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F31" s="1">
         <v>46104</v>
@@ -14038,19 +14048,19 @@
         <v>1062</v>
       </c>
       <c r="U31" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="V31" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="X31" t="s">
         <v>1062</v>
       </c>
       <c r="Y31" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="AA31" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="AB31" t="s">
         <v>736</v>
@@ -14068,7 +14078,7 @@
         <v>903</v>
       </c>
       <c r="AH31" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="AK31">
         <v>3</v>
@@ -14080,7 +14090,7 @@
         <v>3</v>
       </c>
       <c r="AO31" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AP31">
         <v>1</v>
@@ -14107,7 +14117,7 @@
         <v>822</v>
       </c>
       <c r="AZ31" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="BA31" t="s">
         <v>982</v>
@@ -14122,7 +14132,7 @@
         <v>913</v>
       </c>
       <c r="BE31" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="BF31" t="s">
         <v>721</v>
@@ -14134,31 +14144,31 @@
         <v>1083</v>
       </c>
       <c r="BI31" t="s">
+        <v>1192</v>
+      </c>
+      <c r="BJ31" t="s">
         <v>1193</v>
       </c>
-      <c r="BJ31" t="s">
+      <c r="BK31" t="s">
         <v>1194</v>
       </c>
-      <c r="BK31" t="s">
+      <c r="BL31" t="s">
         <v>1195</v>
       </c>
-      <c r="BL31" t="s">
+      <c r="BR31" t="s">
         <v>1196</v>
       </c>
-      <c r="BR31" t="s">
+      <c r="BS31" t="s">
         <v>1197</v>
-      </c>
-      <c r="BS31" t="s">
-        <v>1198</v>
       </c>
       <c r="BT31" t="s">
         <v>695</v>
       </c>
       <c r="BU31" t="s">
+        <v>1198</v>
+      </c>
+      <c r="BV31" t="s">
         <v>1199</v>
-      </c>
-      <c r="BV31" t="s">
-        <v>1200</v>
       </c>
       <c r="CA31" t="s">
         <v>704</v>
@@ -14179,7 +14189,7 @@
         <v>708777590</v>
       </c>
       <c r="YF31" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="YG31" s="1">
         <v>46108.542222222219</v>
@@ -14191,7 +14201,7 @@
         <v>1076</v>
       </c>
       <c r="YN31" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="YO31">
         <v>30</v>
@@ -14208,7 +14218,7 @@
         <v>997</v>
       </c>
       <c r="E32" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="F32" s="1">
         <v>46104</v>
@@ -14238,7 +14248,7 @@
         <v>670</v>
       </c>
       <c r="Q32" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="R32" t="s">
         <v>670</v>
@@ -14250,7 +14260,7 @@
         <v>1062</v>
       </c>
       <c r="Y32" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AB32" t="s">
         <v>736</v>
@@ -14271,7 +14281,7 @@
         <v>674</v>
       </c>
       <c r="AJ32" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="AK32">
         <v>5</v>
@@ -14283,7 +14293,7 @@
         <v>3</v>
       </c>
       <c r="AO32" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AP32">
         <v>1</v>
@@ -14307,7 +14317,7 @@
         <v>737</v>
       </c>
       <c r="AX32" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="AY32" t="s">
         <v>717</v>
@@ -14340,19 +14350,19 @@
         <v>1082</v>
       </c>
       <c r="BI32" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="BJ32" t="s">
         <v>953</v>
       </c>
       <c r="BK32" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="BL32" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="BM32" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="BN32" t="s">
         <v>893</v>
@@ -14364,7 +14374,7 @@
         <v>892</v>
       </c>
       <c r="BQ32" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="BR32" t="s">
         <v>959</v>
@@ -14373,91 +14383,91 @@
         <v>923</v>
       </c>
       <c r="BT32" t="s">
+        <v>1208</v>
+      </c>
+      <c r="BU32" t="s">
         <v>1209</v>
       </c>
-      <c r="BU32" t="s">
+      <c r="BV32" t="s">
         <v>1210</v>
-      </c>
-      <c r="BV32" t="s">
-        <v>1211</v>
       </c>
       <c r="CA32" t="s">
         <v>705</v>
       </c>
       <c r="CB32" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="CC32" t="s">
         <v>705</v>
       </c>
       <c r="CD32" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="CE32" t="s">
         <v>705</v>
       </c>
       <c r="CF32" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="CG32" t="s">
         <v>705</v>
       </c>
       <c r="CH32" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="CI32" t="s">
         <v>705</v>
       </c>
       <c r="CJ32" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="CK32" t="s">
         <v>705</v>
       </c>
       <c r="CL32" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="CM32" t="s">
         <v>705</v>
       </c>
       <c r="CN32" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="CO32" t="s">
         <v>705</v>
       </c>
       <c r="CP32" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="CQ32" t="s">
         <v>705</v>
       </c>
       <c r="CR32" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="CS32" t="s">
         <v>705</v>
       </c>
       <c r="CT32" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="CU32" t="s">
         <v>705</v>
       </c>
       <c r="CV32" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="CW32" t="s">
         <v>705</v>
       </c>
       <c r="CX32" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="YE32">
         <v>708786847</v>
       </c>
       <c r="YF32" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="YG32" s="1">
         <v>46108.547511574077</v>
@@ -14469,7 +14479,7 @@
         <v>1076</v>
       </c>
       <c r="YN32" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="YO32">
         <v>31</v>
@@ -14483,10 +14493,10 @@
         <v>46108.597637685183</v>
       </c>
       <c r="D33" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E33" t="s">
         <v>1226</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1227</v>
       </c>
       <c r="F33" s="1">
         <v>46104</v>
@@ -14531,10 +14541,10 @@
         <v>671</v>
       </c>
       <c r="AG33" t="s">
+        <v>1227</v>
+      </c>
+      <c r="AH33" t="s">
         <v>1228</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>1229</v>
       </c>
       <c r="AI33" t="s">
         <v>673</v>
@@ -14552,7 +14562,7 @@
         <v>2</v>
       </c>
       <c r="AO33" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="AP33">
         <v>1</v>
@@ -14573,25 +14583,25 @@
         <v>1</v>
       </c>
       <c r="AV33" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="AW33" t="s">
         <v>676</v>
       </c>
       <c r="AX33" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="AY33" t="s">
         <v>678</v>
       </c>
       <c r="AZ33" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="BA33" t="s">
         <v>745</v>
       </c>
       <c r="BB33" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="BC33" t="s">
         <v>681</v>
@@ -14609,49 +14619,49 @@
         <v>949</v>
       </c>
       <c r="BH33" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="BI33" t="s">
         <v>687</v>
       </c>
       <c r="BJ33" t="s">
+        <v>1233</v>
+      </c>
+      <c r="BK33" t="s">
         <v>1234</v>
       </c>
-      <c r="BK33" t="s">
+      <c r="BL33" t="s">
         <v>1235</v>
-      </c>
-      <c r="BL33" t="s">
-        <v>1236</v>
       </c>
       <c r="BM33" t="s">
         <v>936</v>
       </c>
       <c r="BN33" t="s">
+        <v>1236</v>
+      </c>
+      <c r="BO33" t="s">
         <v>1237</v>
-      </c>
-      <c r="BO33" t="s">
-        <v>1238</v>
       </c>
       <c r="BP33" t="s">
         <v>922</v>
       </c>
       <c r="BQ33" t="s">
+        <v>1238</v>
+      </c>
+      <c r="BR33" t="s">
+        <v>1233</v>
+      </c>
+      <c r="BS33" t="s">
         <v>1239</v>
       </c>
-      <c r="BR33" t="s">
-        <v>1234</v>
-      </c>
-      <c r="BS33" t="s">
+      <c r="BT33" t="s">
         <v>1240</v>
-      </c>
-      <c r="BT33" t="s">
-        <v>1241</v>
       </c>
       <c r="BU33" t="s">
         <v>719</v>
       </c>
       <c r="BV33" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="CA33" t="s">
         <v>860</v>
@@ -14684,7 +14694,7 @@
         <v>705</v>
       </c>
       <c r="CT33" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="CU33" t="s">
         <v>707</v>
@@ -14699,13 +14709,13 @@
         <v>671</v>
       </c>
       <c r="DN33" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="YE33">
         <v>708800469</v>
       </c>
       <c r="YF33" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="YG33" s="1">
         <v>46108.555972222217</v>
@@ -14717,7 +14727,7 @@
         <v>1076</v>
       </c>
       <c r="YN33" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="YO33">
         <v>32</v>
@@ -14731,10 +14741,10 @@
         <v>46108.601552546294</v>
       </c>
       <c r="D34" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E34" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F34" s="1">
         <v>46104</v>
@@ -14782,7 +14792,7 @@
         <v>671</v>
       </c>
       <c r="AG34" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AH34" t="s">
         <v>764</v>
@@ -14830,7 +14840,7 @@
         <v>843</v>
       </c>
       <c r="AY34" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="AZ34" t="s">
         <v>764</v>
@@ -14845,7 +14855,7 @@
         <v>845</v>
       </c>
       <c r="BD34" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="BE34" t="s">
         <v>913</v>
@@ -14854,34 +14864,34 @@
         <v>889</v>
       </c>
       <c r="BG34" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="BH34" t="s">
         <v>1083</v>
       </c>
       <c r="BI34" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="BJ34" t="s">
         <v>687</v>
       </c>
       <c r="BK34" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="BL34" t="s">
         <v>898</v>
       </c>
       <c r="BM34" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="BN34" t="s">
         <v>919</v>
       </c>
       <c r="BO34" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="BP34" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="BQ34" t="s">
         <v>873</v>
@@ -14890,16 +14900,16 @@
         <v>1006</v>
       </c>
       <c r="BS34" t="s">
+        <v>1252</v>
+      </c>
+      <c r="BT34" t="s">
         <v>1253</v>
       </c>
-      <c r="BT34" t="s">
+      <c r="BU34" t="s">
         <v>1254</v>
       </c>
-      <c r="BU34" t="s">
-        <v>1255</v>
-      </c>
       <c r="BV34" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="CA34" t="s">
         <v>699</v>
@@ -14911,13 +14921,13 @@
         <v>705</v>
       </c>
       <c r="CF34" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="CG34" t="s">
         <v>708</v>
       </c>
       <c r="CI34" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="CK34" t="s">
         <v>776</v>
@@ -14950,7 +14960,7 @@
         <v>708807377</v>
       </c>
       <c r="YF34" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="YG34" s="1">
         <v>46108.559884259259</v>
@@ -14962,7 +14972,7 @@
         <v>1076</v>
       </c>
       <c r="YN34" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="YO34">
         <v>33</v>
@@ -14976,10 +14986,10 @@
         <v>46108.74425895833</v>
       </c>
       <c r="D35" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E35" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="F35" s="1">
         <v>46104</v>
@@ -15048,7 +15058,7 @@
         <v>7</v>
       </c>
       <c r="AO35" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="AP35">
         <v>1</v>
@@ -15087,7 +15097,7 @@
         <v>843</v>
       </c>
       <c r="BC35" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="BD35" t="s">
         <v>742</v>
@@ -15108,19 +15118,19 @@
         <v>969</v>
       </c>
       <c r="BJ35" t="s">
+        <v>1262</v>
+      </c>
+      <c r="BK35" t="s">
         <v>1263</v>
       </c>
-      <c r="BK35" t="s">
+      <c r="BL35" t="s">
         <v>1264</v>
-      </c>
-      <c r="BL35" t="s">
-        <v>1265</v>
       </c>
       <c r="BM35" t="s">
         <v>1068</v>
       </c>
       <c r="BN35" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="BO35" t="s">
         <v>936</v>
@@ -15135,16 +15145,16 @@
         <v>1068</v>
       </c>
       <c r="BS35" t="s">
+        <v>1265</v>
+      </c>
+      <c r="BT35" t="s">
         <v>1266</v>
       </c>
-      <c r="BT35" t="s">
+      <c r="BU35" t="s">
         <v>1267</v>
       </c>
-      <c r="BU35" t="s">
+      <c r="BV35" t="s">
         <v>1268</v>
-      </c>
-      <c r="BV35" t="s">
-        <v>1269</v>
       </c>
       <c r="CA35" t="s">
         <v>703</v>
@@ -15171,10 +15181,10 @@
         <v>860</v>
       </c>
       <c r="CQ35" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="CS35" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="CU35" t="s">
         <v>756</v>
@@ -15195,13 +15205,13 @@
         <v>671</v>
       </c>
       <c r="DN35" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="YE35">
         <v>708815648</v>
       </c>
       <c r="YF35" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="YG35" s="1">
         <v>46108.56449074074</v>
@@ -15213,7 +15223,7 @@
         <v>1076</v>
       </c>
       <c r="YN35" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="YO35">
         <v>34</v>
@@ -15227,10 +15237,10 @@
         <v>46108.609401018519</v>
       </c>
       <c r="D36" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E36" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F36" s="1">
         <v>46104</v>
@@ -15266,7 +15276,7 @@
         <v>982</v>
       </c>
       <c r="T36" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="X36" t="s">
         <v>1062</v>
@@ -15296,7 +15306,7 @@
         <v>5</v>
       </c>
       <c r="AO36" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="AP36">
         <v>1</v>
@@ -15335,13 +15345,13 @@
         <v>913</v>
       </c>
       <c r="BD36" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="BE36" t="s">
         <v>720</v>
       </c>
       <c r="BF36" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="BG36" t="s">
         <v>723</v>
@@ -15350,37 +15360,37 @@
         <v>895</v>
       </c>
       <c r="BI36" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="BJ36" t="s">
+        <v>1275</v>
+      </c>
+      <c r="BK36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="BL36" t="s">
         <v>1276</v>
-      </c>
-      <c r="BK36" t="s">
-        <v>1263</v>
-      </c>
-      <c r="BL36" t="s">
-        <v>1277</v>
       </c>
       <c r="BM36" t="s">
         <v>936</v>
       </c>
       <c r="BN36" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="BO36" t="s">
         <v>893</v>
       </c>
       <c r="BP36" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="BR36" t="s">
         <v>895</v>
       </c>
       <c r="BS36" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="BT36" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="BU36" t="s">
         <v>747</v>
@@ -15392,7 +15402,7 @@
         <v>801</v>
       </c>
       <c r="CC36" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="CE36" t="s">
         <v>699</v>
@@ -15404,7 +15414,7 @@
         <v>708821639</v>
       </c>
       <c r="YF36" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="YG36" s="1">
         <v>46108.567731481482</v>
@@ -15416,7 +15426,7 @@
         <v>1076</v>
       </c>
       <c r="YN36" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="YO36">
         <v>35</v>
@@ -15430,10 +15440,10 @@
         <v>46108.613609583343</v>
       </c>
       <c r="D37" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E37" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F37" s="1">
         <v>46104</v>
@@ -15463,7 +15473,7 @@
         <v>670</v>
       </c>
       <c r="Q37" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="R37" t="s">
         <v>670</v>
@@ -15472,22 +15482,22 @@
         <v>1062</v>
       </c>
       <c r="U37" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="X37" t="s">
         <v>1062</v>
       </c>
       <c r="Y37" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AB37" t="s">
         <v>671</v>
       </c>
       <c r="AG37" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="AH37" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="AI37" t="s">
         <v>678</v>
@@ -15505,7 +15515,7 @@
         <v>7</v>
       </c>
       <c r="AO37" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="AP37">
         <v>1</v>
@@ -15526,13 +15536,13 @@
         <v>1</v>
       </c>
       <c r="AV37" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="AW37" t="s">
         <v>737</v>
       </c>
       <c r="AX37" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="AY37" t="s">
         <v>682</v>
@@ -15547,7 +15557,7 @@
         <v>679</v>
       </c>
       <c r="BC37" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="BD37" t="s">
         <v>889</v>
@@ -15556,10 +15566,10 @@
         <v>721</v>
       </c>
       <c r="BF37" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="BG37" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="BH37" t="s">
         <v>895</v>
@@ -15568,31 +15578,31 @@
         <v>1011</v>
       </c>
       <c r="BJ37" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="BK37" t="s">
+        <v>1288</v>
+      </c>
+      <c r="BL37" t="s">
         <v>1289</v>
-      </c>
-      <c r="BL37" t="s">
-        <v>1290</v>
       </c>
       <c r="BM37" t="s">
         <v>936</v>
       </c>
       <c r="BN37" t="s">
+        <v>1290</v>
+      </c>
+      <c r="BO37" t="s">
+        <v>1155</v>
+      </c>
+      <c r="BP37" t="s">
         <v>1291</v>
       </c>
-      <c r="BO37" t="s">
-        <v>1156</v>
-      </c>
-      <c r="BP37" t="s">
+      <c r="BQ37" t="s">
         <v>1292</v>
       </c>
-      <c r="BQ37" t="s">
+      <c r="BR37" t="s">
         <v>1293</v>
-      </c>
-      <c r="BR37" t="s">
-        <v>1294</v>
       </c>
       <c r="BS37" t="s">
         <v>878</v>
@@ -15601,7 +15611,7 @@
         <v>942</v>
       </c>
       <c r="BU37" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="BV37" t="s">
         <v>747</v>
@@ -15619,28 +15629,28 @@
         <v>705</v>
       </c>
       <c r="CH37" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="CI37" t="s">
         <v>801</v>
       </c>
       <c r="CK37" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="DM37" t="s">
         <v>671</v>
       </c>
       <c r="DN37" t="s">
+        <v>1296</v>
+      </c>
+      <c r="DO37" t="s">
         <v>1297</v>
-      </c>
-      <c r="DO37" t="s">
-        <v>1298</v>
       </c>
       <c r="YE37">
         <v>708830903</v>
       </c>
       <c r="YF37" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="YG37" s="1">
         <v>46108.571944444448</v>
@@ -15652,7 +15662,7 @@
         <v>1076</v>
       </c>
       <c r="YN37" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="YO37">
         <v>36</v>
@@ -15666,10 +15676,10 @@
         <v>46108.618302453702</v>
       </c>
       <c r="D38" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E38" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F38" s="1">
         <v>46104</v>
@@ -15696,7 +15706,7 @@
         <v>670</v>
       </c>
       <c r="P38" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="Q38" t="s">
         <v>670</v>
@@ -15714,7 +15724,7 @@
         <v>736</v>
       </c>
       <c r="AC38" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="AG38" t="s">
         <v>674</v>
@@ -15735,7 +15745,7 @@
         <v>7</v>
       </c>
       <c r="AO38" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="AP38">
         <v>1</v>
@@ -15756,7 +15766,7 @@
         <v>1</v>
       </c>
       <c r="AV38" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="AX38" t="s">
         <v>679</v>
@@ -15771,7 +15781,7 @@
         <v>674</v>
       </c>
       <c r="BB38" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="BC38" t="s">
         <v>723</v>
@@ -15783,7 +15793,7 @@
         <v>808</v>
       </c>
       <c r="BF38" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="BG38" t="s">
         <v>845</v>
@@ -15792,16 +15802,16 @@
         <v>942</v>
       </c>
       <c r="BI38" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="BJ38" t="s">
         <v>972</v>
       </c>
       <c r="BK38" t="s">
+        <v>1304</v>
+      </c>
+      <c r="BL38" t="s">
         <v>1305</v>
-      </c>
-      <c r="BL38" t="s">
-        <v>1306</v>
       </c>
       <c r="BM38" t="s">
         <v>1087</v>
@@ -15810,28 +15820,28 @@
         <v>851</v>
       </c>
       <c r="BO38" t="s">
+        <v>1306</v>
+      </c>
+      <c r="BP38" t="s">
         <v>1307</v>
       </c>
-      <c r="BP38" t="s">
+      <c r="BQ38" t="s">
         <v>1308</v>
       </c>
-      <c r="BQ38" t="s">
+      <c r="BR38" t="s">
         <v>1309</v>
       </c>
-      <c r="BR38" t="s">
+      <c r="BS38" t="s">
+        <v>1208</v>
+      </c>
+      <c r="BT38" t="s">
         <v>1310</v>
-      </c>
-      <c r="BS38" t="s">
-        <v>1209</v>
-      </c>
-      <c r="BT38" t="s">
-        <v>1311</v>
       </c>
       <c r="BU38" t="s">
         <v>747</v>
       </c>
       <c r="BV38" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="CA38" t="s">
         <v>1039</v>
@@ -15846,7 +15856,7 @@
         <v>705</v>
       </c>
       <c r="CH38" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="CI38" t="s">
         <v>756</v>
@@ -15864,19 +15874,19 @@
         <v>705</v>
       </c>
       <c r="CR38" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="CS38" t="s">
         <v>705</v>
       </c>
       <c r="CT38" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="CU38" t="s">
         <v>705</v>
       </c>
       <c r="CV38" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="CW38" t="s">
         <v>753</v>
@@ -15885,7 +15895,7 @@
         <v>708839121</v>
       </c>
       <c r="YF38" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="YG38" s="1">
         <v>46108.576631944437</v>
@@ -15897,7 +15907,7 @@
         <v>1076</v>
       </c>
       <c r="YN38" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="YO38">
         <v>37</v>
@@ -15911,10 +15921,10 @@
         <v>46108.621410046297</v>
       </c>
       <c r="D39" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E39" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F39" s="1">
         <v>46104</v>
@@ -16019,7 +16029,7 @@
         <v>673</v>
       </c>
       <c r="BC39" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="BD39" t="s">
         <v>683</v>
@@ -16034,22 +16044,22 @@
         <v>913</v>
       </c>
       <c r="BH39" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="BI39" t="s">
         <v>1011</v>
       </c>
       <c r="BJ39" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="BK39" t="s">
         <v>853</v>
       </c>
       <c r="BL39" t="s">
+        <v>1321</v>
+      </c>
+      <c r="BM39" t="s">
         <v>1322</v>
-      </c>
-      <c r="BM39" t="s">
-        <v>1323</v>
       </c>
       <c r="BN39" t="s">
         <v>915</v>
@@ -16058,31 +16068,31 @@
         <v>873</v>
       </c>
       <c r="BP39" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="BQ39" t="s">
         <v>692</v>
       </c>
       <c r="BR39" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="BS39" t="s">
         <v>907</v>
       </c>
       <c r="BT39" t="s">
+        <v>1324</v>
+      </c>
+      <c r="BU39" t="s">
         <v>1325</v>
       </c>
-      <c r="BU39" t="s">
+      <c r="BV39" t="s">
         <v>1326</v>
-      </c>
-      <c r="BV39" t="s">
-        <v>1327</v>
       </c>
       <c r="CA39" t="s">
         <v>705</v>
       </c>
       <c r="CB39" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="CC39" t="s">
         <v>699</v>
@@ -16106,7 +16116,7 @@
         <v>708844440</v>
       </c>
       <c r="YF39" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="YG39" s="1">
         <v>46108.579745370371</v>
@@ -16118,7 +16128,7 @@
         <v>1076</v>
       </c>
       <c r="YN39" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="YO39">
         <v>38</v>
@@ -16132,10 +16142,10 @@
         <v>46108.624228969908</v>
       </c>
       <c r="D40" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E40" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F40" s="1">
         <v>46104</v>
@@ -16192,7 +16202,7 @@
         <v>2</v>
       </c>
       <c r="AO40" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="AP40">
         <v>0</v>
@@ -16237,7 +16247,7 @@
         <v>681</v>
       </c>
       <c r="BE40" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="BF40" t="s">
         <v>683</v>
@@ -16246,28 +16256,28 @@
         <v>889</v>
       </c>
       <c r="BH40" t="s">
+        <v>1332</v>
+      </c>
+      <c r="BI40" t="s">
         <v>1333</v>
       </c>
-      <c r="BI40" t="s">
+      <c r="BJ40" t="s">
+        <v>1182</v>
+      </c>
+      <c r="BK40" t="s">
         <v>1334</v>
       </c>
-      <c r="BJ40" t="s">
-        <v>1183</v>
-      </c>
-      <c r="BK40" t="s">
+      <c r="BL40" t="s">
         <v>1335</v>
       </c>
-      <c r="BL40" t="s">
+      <c r="BM40" t="s">
         <v>1336</v>
       </c>
-      <c r="BM40" t="s">
+      <c r="BN40" t="s">
         <v>1337</v>
       </c>
-      <c r="BN40" t="s">
+      <c r="BO40" t="s">
         <v>1338</v>
-      </c>
-      <c r="BO40" t="s">
-        <v>1339</v>
       </c>
       <c r="BP40" t="s">
         <v>851</v>
@@ -16276,31 +16286,31 @@
         <v>915</v>
       </c>
       <c r="BR40" t="s">
+        <v>1339</v>
+      </c>
+      <c r="BS40" t="s">
+        <v>1323</v>
+      </c>
+      <c r="BT40" t="s">
         <v>1340</v>
       </c>
-      <c r="BS40" t="s">
-        <v>1324</v>
-      </c>
-      <c r="BT40" t="s">
+      <c r="BU40" t="s">
         <v>1341</v>
       </c>
-      <c r="BU40" t="s">
-        <v>1342</v>
-      </c>
       <c r="BV40" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="CA40" t="s">
         <v>705</v>
       </c>
       <c r="CB40" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="YE40">
         <v>708849164</v>
       </c>
       <c r="YF40" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="YG40" s="1">
         <v>46108.582557870373</v>
@@ -16312,7 +16322,7 @@
         <v>1076</v>
       </c>
       <c r="YN40" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="YO40">
         <v>39</v>
@@ -16326,10 +16336,10 @@
         <v>46108.627790509257</v>
       </c>
       <c r="D41" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E41" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="F41" s="1">
         <v>46104</v>
@@ -16428,7 +16438,7 @@
         <v>822</v>
       </c>
       <c r="BA41" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="BB41" t="s">
         <v>674</v>
@@ -16443,85 +16453,85 @@
         <v>742</v>
       </c>
       <c r="BF41" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="BG41" t="s">
         <v>682</v>
       </c>
       <c r="BH41" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="BI41" t="s">
         <v>958</v>
       </c>
       <c r="BJ41" t="s">
+        <v>1347</v>
+      </c>
+      <c r="BK41" t="s">
         <v>1348</v>
       </c>
-      <c r="BK41" t="s">
+      <c r="BL41" t="s">
         <v>1349</v>
       </c>
-      <c r="BL41" t="s">
+      <c r="BM41" t="s">
         <v>1350</v>
-      </c>
-      <c r="BM41" t="s">
-        <v>1351</v>
       </c>
       <c r="BN41" t="s">
         <v>958</v>
       </c>
       <c r="BO41" t="s">
+        <v>1351</v>
+      </c>
+      <c r="BP41" t="s">
+        <v>1338</v>
+      </c>
+      <c r="BQ41" t="s">
         <v>1352</v>
       </c>
-      <c r="BP41" t="s">
-        <v>1339</v>
-      </c>
-      <c r="BQ41" t="s">
-        <v>1353</v>
-      </c>
       <c r="BR41" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="BS41" t="s">
         <v>958</v>
       </c>
       <c r="BT41" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="BU41" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="BV41" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="CA41" t="s">
         <v>705</v>
       </c>
       <c r="CB41" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="CC41" t="s">
         <v>705</v>
       </c>
       <c r="CD41" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="CE41" t="s">
         <v>705</v>
       </c>
       <c r="CF41" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="CG41" t="s">
         <v>705</v>
       </c>
       <c r="CH41" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="YE41">
         <v>708854990</v>
       </c>
       <c r="YF41" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="YG41" s="1">
         <v>46108.586122685178</v>
@@ -16533,7 +16543,7 @@
         <v>1076</v>
       </c>
       <c r="YN41" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="YO41">
         <v>40</v>
@@ -16547,10 +16557,10 @@
         <v>46108.631550347221</v>
       </c>
       <c r="D42" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E42" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F42" s="1">
         <v>46104</v>
@@ -16670,34 +16680,34 @@
         <v>687</v>
       </c>
       <c r="BI42" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="BJ42" t="s">
         <v>958</v>
       </c>
       <c r="BM42" t="s">
+        <v>1362</v>
+      </c>
+      <c r="BN42" t="s">
+        <v>1361</v>
+      </c>
+      <c r="BO42" t="s">
+        <v>1173</v>
+      </c>
+      <c r="BP42" t="s">
         <v>1363</v>
       </c>
-      <c r="BN42" t="s">
-        <v>1362</v>
-      </c>
-      <c r="BO42" t="s">
-        <v>1174</v>
-      </c>
-      <c r="BP42" t="s">
+      <c r="BR42" t="s">
         <v>1364</v>
-      </c>
-      <c r="BR42" t="s">
-        <v>1365</v>
       </c>
       <c r="BS42" t="s">
         <v>895</v>
       </c>
       <c r="BT42" t="s">
+        <v>1365</v>
+      </c>
+      <c r="BU42" t="s">
         <v>1366</v>
-      </c>
-      <c r="BU42" t="s">
-        <v>1367</v>
       </c>
       <c r="BV42" t="s">
         <v>719</v>
@@ -16724,7 +16734,7 @@
         <v>708861285</v>
       </c>
       <c r="YF42" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="YG42" s="1">
         <v>46108.589884259258</v>
@@ -16736,7 +16746,7 @@
         <v>1076</v>
       </c>
       <c r="YN42" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="YO42">
         <v>41</v>
@@ -16750,10 +16760,10 @@
         <v>46108.634592789349</v>
       </c>
       <c r="D43" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E43" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="F43" s="1">
         <v>46104</v>
@@ -16876,13 +16886,13 @@
         <v>914</v>
       </c>
       <c r="BM43" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="BN43" t="s">
         <v>873</v>
       </c>
       <c r="BO43" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="BP43" t="s">
         <v>851</v>
@@ -16891,16 +16901,16 @@
         <v>851</v>
       </c>
       <c r="BS43" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="BT43" t="s">
         <v>939</v>
       </c>
       <c r="BU43" t="s">
+        <v>1373</v>
+      </c>
+      <c r="BV43" t="s">
         <v>1374</v>
-      </c>
-      <c r="BV43" t="s">
-        <v>1375</v>
       </c>
       <c r="CA43" t="s">
         <v>700</v>
@@ -16930,7 +16940,7 @@
         <v>708866715</v>
       </c>
       <c r="YF43" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="YG43" s="1">
         <v>46108.592928240738</v>
@@ -16942,7 +16952,7 @@
         <v>1076</v>
       </c>
       <c r="YN43" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="YO43">
         <v>42</v>
@@ -16956,10 +16966,10 @@
         <v>46108.637685081019</v>
       </c>
       <c r="D44" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E44" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F44" s="1">
         <v>46104</v>
@@ -17040,7 +17050,7 @@
         <v>676</v>
       </c>
       <c r="AX44" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="AY44" t="s">
         <v>966</v>
@@ -17064,7 +17074,7 @@
         <v>1001</v>
       </c>
       <c r="BF44" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="BG44" t="s">
         <v>682</v>
@@ -17073,16 +17083,16 @@
         <v>687</v>
       </c>
       <c r="BI44" t="s">
+        <v>1379</v>
+      </c>
+      <c r="BJ44" t="s">
         <v>1380</v>
-      </c>
-      <c r="BJ44" t="s">
-        <v>1381</v>
       </c>
       <c r="BK44" t="s">
         <v>895</v>
       </c>
       <c r="BL44" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="BM44" t="s">
         <v>936</v>
@@ -17091,7 +17101,7 @@
         <v>893</v>
       </c>
       <c r="BO44" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="BP44" t="s">
         <v>955</v>
@@ -17103,16 +17113,16 @@
         <v>907</v>
       </c>
       <c r="BS44" t="s">
+        <v>1383</v>
+      </c>
+      <c r="BT44" t="s">
         <v>1384</v>
       </c>
-      <c r="BT44" t="s">
+      <c r="BU44" t="s">
         <v>1385</v>
       </c>
-      <c r="BU44" t="s">
-        <v>1386</v>
-      </c>
       <c r="BV44" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="CA44" t="s">
         <v>699</v>
@@ -17139,7 +17149,7 @@
         <v>708871817</v>
       </c>
       <c r="YF44" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="YG44" s="1">
         <v>46108.596018518518</v>
@@ -17151,7 +17161,7 @@
         <v>1076</v>
       </c>
       <c r="YN44" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="YO44">
         <v>43</v>
@@ -17165,10 +17175,10 @@
         <v>46108.641395474537</v>
       </c>
       <c r="D45" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E45" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="F45" s="1">
         <v>46104</v>
@@ -17267,7 +17277,7 @@
         <v>678</v>
       </c>
       <c r="BC45" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="BD45" t="s">
         <v>721</v>
@@ -17288,37 +17298,37 @@
         <v>972</v>
       </c>
       <c r="BJ45" t="s">
+        <v>1389</v>
+      </c>
+      <c r="BK45" t="s">
         <v>1390</v>
       </c>
-      <c r="BK45" t="s">
-        <v>1391</v>
-      </c>
       <c r="BL45" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="BM45" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="BN45" t="s">
         <v>893</v>
       </c>
       <c r="BO45" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="BP45" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="BR45" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="BS45" t="s">
         <v>895</v>
       </c>
       <c r="BT45" t="s">
+        <v>1392</v>
+      </c>
+      <c r="BU45" t="s">
         <v>1393</v>
-      </c>
-      <c r="BU45" t="s">
-        <v>1394</v>
       </c>
       <c r="CA45" t="s">
         <v>801</v>
@@ -17348,7 +17358,7 @@
         <v>708878683</v>
       </c>
       <c r="YF45" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="YG45" s="1">
         <v>46108.599733796298</v>
@@ -17360,7 +17370,7 @@
         <v>1076</v>
       </c>
       <c r="YN45" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="YO45">
         <v>44</v>
@@ -17374,10 +17384,10 @@
         <v>46108.644422233803</v>
       </c>
       <c r="D46" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E46" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="F46" s="1">
         <v>46104</v>
@@ -17491,19 +17501,19 @@
         <v>680</v>
       </c>
       <c r="BH46" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="BI46" t="s">
         <v>1082</v>
       </c>
       <c r="BJ46" t="s">
+        <v>1398</v>
+      </c>
+      <c r="BK46" t="s">
         <v>1399</v>
       </c>
-      <c r="BK46" t="s">
+      <c r="BL46" t="s">
         <v>1400</v>
-      </c>
-      <c r="BL46" t="s">
-        <v>1401</v>
       </c>
       <c r="BM46" t="s">
         <v>1051</v>
@@ -17515,7 +17525,7 @@
         <v>873</v>
       </c>
       <c r="BP46" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="BQ46" t="s">
         <v>919</v>
@@ -17527,10 +17537,10 @@
         <v>922</v>
       </c>
       <c r="BT46" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="BU46" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="CA46" t="s">
         <v>801</v>
@@ -17557,7 +17567,7 @@
         <v>708884299</v>
       </c>
       <c r="YF46" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="YG46" s="1">
         <v>46108.602754629632</v>
@@ -17569,7 +17579,7 @@
         <v>1076</v>
       </c>
       <c r="YN46" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="YO46">
         <v>45</v>
@@ -17583,10 +17593,10 @@
         <v>46108.647262696759</v>
       </c>
       <c r="D47" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E47" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="F47" s="1">
         <v>46104</v>
@@ -17685,7 +17695,7 @@
         <v>889</v>
       </c>
       <c r="BE47" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="BF47" t="s">
         <v>845</v>
@@ -17700,34 +17710,34 @@
         <v>959</v>
       </c>
       <c r="BJ47" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="BK47" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="BL47" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="BM47" t="s">
         <v>915</v>
       </c>
       <c r="BN47" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="BO47" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="BP47" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="BQ47" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="BR47" t="s">
         <v>924</v>
       </c>
       <c r="BS47" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="BT47" t="s">
         <v>907</v>
@@ -17763,7 +17773,7 @@
         <v>708889333</v>
       </c>
       <c r="YF47" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="YG47" s="1">
         <v>46108.60560185185</v>
@@ -17775,7 +17785,7 @@
         <v>1076</v>
       </c>
       <c r="YN47" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="YO47">
         <v>46</v>
@@ -17789,10 +17799,10 @@
         <v>46108.652282546303</v>
       </c>
       <c r="D48" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E48" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F48" s="1">
         <v>46104</v>
@@ -17840,13 +17850,13 @@
         <v>677</v>
       </c>
       <c r="AH48" t="s">
+        <v>1413</v>
+      </c>
+      <c r="AI48" t="s">
         <v>1414</v>
       </c>
-      <c r="AI48" t="s">
+      <c r="AJ48" t="s">
         <v>1415</v>
-      </c>
-      <c r="AJ48" t="s">
-        <v>1416</v>
       </c>
       <c r="AL48">
         <v>7</v>
@@ -17897,10 +17907,10 @@
         <v>913</v>
       </c>
       <c r="BE48" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="BF48" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="BG48" t="s">
         <v>683</v>
@@ -17915,16 +17925,16 @@
         <v>972</v>
       </c>
       <c r="BK48" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="BL48" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="BM48" t="s">
         <v>936</v>
       </c>
       <c r="BN48" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="BO48" t="s">
         <v>955</v>
@@ -17933,7 +17943,7 @@
         <v>956</v>
       </c>
       <c r="BQ48" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="BR48" t="s">
         <v>976</v>
@@ -17942,10 +17952,10 @@
         <v>1091</v>
       </c>
       <c r="BT48" t="s">
+        <v>1420</v>
+      </c>
+      <c r="BU48" t="s">
         <v>1421</v>
-      </c>
-      <c r="BU48" t="s">
-        <v>1422</v>
       </c>
       <c r="BV48" t="s">
         <v>923</v>
@@ -17978,19 +17988,19 @@
         <v>779</v>
       </c>
       <c r="CS48" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="DM48" t="s">
         <v>671</v>
       </c>
       <c r="DN48" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="YE48">
         <v>708897199</v>
       </c>
       <c r="YF48" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="YG48" s="1">
         <v>46108.610613425917</v>
@@ -18002,7 +18012,7 @@
         <v>1076</v>
       </c>
       <c r="YN48" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="YO48">
         <v>47</v>
@@ -18016,10 +18026,10 @@
         <v>46108.746890173607</v>
       </c>
       <c r="D49" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E49" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F49" s="1">
         <v>46104</v>
@@ -18043,37 +18053,37 @@
         <v>2005</v>
       </c>
       <c r="O49" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="P49" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="Q49" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="R49" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="T49" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="X49" t="s">
         <v>1062</v>
       </c>
       <c r="Y49" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="AB49" t="s">
         <v>736</v>
       </c>
       <c r="AC49" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="AG49" t="s">
         <v>674</v>
       </c>
       <c r="AH49" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="AK49">
         <v>3</v>
@@ -18085,7 +18095,7 @@
         <v>3</v>
       </c>
       <c r="AO49" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="AP49">
         <v>1</v>
@@ -18106,7 +18116,7 @@
         <v>1</v>
       </c>
       <c r="AV49" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="AW49" t="s">
         <v>838</v>
@@ -18127,7 +18137,7 @@
         <v>677</v>
       </c>
       <c r="BC49" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="BD49" t="s">
         <v>674</v>
@@ -18142,55 +18152,55 @@
         <v>913</v>
       </c>
       <c r="BH49" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="BI49" t="s">
+        <v>1429</v>
+      </c>
+      <c r="BJ49" t="s">
         <v>1430</v>
       </c>
-      <c r="BJ49" t="s">
+      <c r="BK49" t="s">
         <v>1431</v>
       </c>
-      <c r="BK49" t="s">
+      <c r="BL49" t="s">
         <v>1432</v>
       </c>
-      <c r="BL49" t="s">
+      <c r="BM49" t="s">
         <v>1433</v>
       </c>
-      <c r="BM49" t="s">
+      <c r="BN49" t="s">
         <v>1434</v>
-      </c>
-      <c r="BN49" t="s">
-        <v>1435</v>
       </c>
       <c r="BO49" t="s">
         <v>936</v>
       </c>
       <c r="BP49" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="BQ49" t="s">
         <v>955</v>
       </c>
       <c r="BR49" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="BS49" t="s">
         <v>719</v>
       </c>
       <c r="BT49" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="BU49" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="BV49" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="CA49" t="s">
         <v>705</v>
       </c>
       <c r="CB49" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="CC49" t="s">
         <v>801</v>
@@ -18205,7 +18215,7 @@
         <v>705</v>
       </c>
       <c r="CJ49" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="CK49" t="s">
         <v>757</v>
@@ -18214,13 +18224,13 @@
         <v>705</v>
       </c>
       <c r="CN49" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="YE49">
         <v>708904427</v>
       </c>
       <c r="YF49" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="YG49" s="1">
         <v>46108.615011574067</v>
@@ -18232,7 +18242,7 @@
         <v>1076</v>
       </c>
       <c r="YN49" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="YO49">
         <v>48</v>
@@ -18246,10 +18256,10 @@
         <v>46108.743401770836</v>
       </c>
       <c r="D50" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E50" t="s">
         <v>1444</v>
-      </c>
-      <c r="E50" t="s">
-        <v>1445</v>
       </c>
       <c r="F50" s="1">
         <v>46105</v>
@@ -18300,7 +18310,7 @@
         <v>682</v>
       </c>
       <c r="AI50" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="AJ50" t="s">
         <v>674</v>
@@ -18348,7 +18358,7 @@
         <v>678</v>
       </c>
       <c r="BA50" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BB50" t="s">
         <v>719</v>
@@ -18372,16 +18382,16 @@
         <v>687</v>
       </c>
       <c r="BI50" t="s">
+        <v>1447</v>
+      </c>
+      <c r="BJ50" t="s">
         <v>1448</v>
-      </c>
-      <c r="BJ50" t="s">
-        <v>1449</v>
       </c>
       <c r="BK50" t="s">
         <v>870</v>
       </c>
       <c r="BL50" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="BM50" t="s">
         <v>936</v>
@@ -18396,7 +18406,7 @@
         <v>958</v>
       </c>
       <c r="BQ50" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="BR50" t="s">
         <v>922</v>
@@ -18405,22 +18415,22 @@
         <v>881</v>
       </c>
       <c r="BT50" t="s">
+        <v>1449</v>
+      </c>
+      <c r="BU50" t="s">
         <v>1450</v>
       </c>
-      <c r="BU50" t="s">
+      <c r="BV50" t="s">
         <v>1451</v>
       </c>
-      <c r="BV50" t="s">
+      <c r="CA50" t="s">
         <v>1452</v>
-      </c>
-      <c r="CA50" t="s">
-        <v>1453</v>
       </c>
       <c r="CC50" t="s">
         <v>705</v>
       </c>
       <c r="CD50" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="CE50" t="s">
         <v>701</v>
@@ -18465,13 +18475,13 @@
         <v>671</v>
       </c>
       <c r="DN50" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="YE50">
         <v>708937924</v>
       </c>
       <c r="YF50" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="YG50" s="1">
         <v>46108.640439814822</v>
@@ -18483,7 +18493,7 @@
         <v>1076</v>
       </c>
       <c r="YN50" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="YO50">
         <v>49</v>
@@ -18497,10 +18507,10 @@
         <v>46108.686105370369</v>
       </c>
       <c r="D51" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E51" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F51" s="1">
         <v>46105</v>
@@ -18623,7 +18633,7 @@
         <v>687</v>
       </c>
       <c r="BI51" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="BJ51" t="s">
         <v>1083</v>
@@ -18632,40 +18642,40 @@
         <v>891</v>
       </c>
       <c r="BM51" t="s">
+        <v>1459</v>
+      </c>
+      <c r="BN51" t="s">
         <v>1460</v>
       </c>
-      <c r="BN51" t="s">
+      <c r="BO51" t="s">
+        <v>1277</v>
+      </c>
+      <c r="BP51" t="s">
         <v>1461</v>
       </c>
-      <c r="BO51" t="s">
-        <v>1278</v>
-      </c>
-      <c r="BP51" t="s">
+      <c r="BQ51" t="s">
+        <v>1193</v>
+      </c>
+      <c r="BR51" t="s">
+        <v>1392</v>
+      </c>
+      <c r="BS51" t="s">
         <v>1462</v>
-      </c>
-      <c r="BQ51" t="s">
-        <v>1194</v>
-      </c>
-      <c r="BR51" t="s">
-        <v>1393</v>
-      </c>
-      <c r="BS51" t="s">
-        <v>1463</v>
       </c>
       <c r="BT51" t="s">
         <v>772</v>
       </c>
       <c r="BU51" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="BV51" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="CA51" t="s">
         <v>708</v>
       </c>
       <c r="CC51" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="CE51" t="s">
         <v>733</v>
@@ -18677,13 +18687,13 @@
         <v>705</v>
       </c>
       <c r="CJ51" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="CK51" t="s">
         <v>757</v>
       </c>
       <c r="CM51" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="CO51" t="s">
         <v>702</v>
@@ -18695,7 +18705,7 @@
         <v>705</v>
       </c>
       <c r="CT51" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="CU51" t="s">
         <v>776</v>
@@ -18710,13 +18720,13 @@
         <v>671</v>
       </c>
       <c r="DN51" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="YE51">
         <v>708943371</v>
       </c>
       <c r="YF51" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="YG51" s="1">
         <v>46108.644432870373</v>
@@ -18728,7 +18738,7 @@
         <v>1076</v>
       </c>
       <c r="YN51" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="YO51">
         <v>50</v>
@@ -18742,10 +18752,10 @@
         <v>46108.743022164352</v>
       </c>
       <c r="D52" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E52" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="F52" s="1">
         <v>46105</v>
@@ -18781,13 +18791,13 @@
         <v>670</v>
       </c>
       <c r="T52" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="X52" t="s">
         <v>1062</v>
       </c>
       <c r="Y52" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="AB52" t="s">
         <v>736</v>
@@ -18847,7 +18857,7 @@
         <v>743</v>
       </c>
       <c r="BB52" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BC52" t="s">
         <v>680</v>
@@ -18856,7 +18866,7 @@
         <v>682</v>
       </c>
       <c r="BH52" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="BI52" t="s">
         <v>972</v>
@@ -18868,34 +18878,34 @@
         <v>853</v>
       </c>
       <c r="BL52" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="BM52" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="BN52" t="s">
         <v>936</v>
       </c>
       <c r="BO52" t="s">
+        <v>1473</v>
+      </c>
+      <c r="BP52" t="s">
+        <v>1118</v>
+      </c>
+      <c r="BQ52" t="s">
+        <v>1154</v>
+      </c>
+      <c r="BR52" t="s">
+        <v>1322</v>
+      </c>
+      <c r="BS52" t="s">
         <v>1474</v>
       </c>
-      <c r="BP52" t="s">
-        <v>1119</v>
-      </c>
-      <c r="BQ52" t="s">
-        <v>1155</v>
-      </c>
-      <c r="BR52" t="s">
-        <v>1323</v>
-      </c>
-      <c r="BS52" t="s">
+      <c r="BT52" t="s">
         <v>1475</v>
       </c>
-      <c r="BT52" t="s">
+      <c r="BU52" t="s">
         <v>1476</v>
-      </c>
-      <c r="BU52" t="s">
-        <v>1477</v>
       </c>
       <c r="BV52" t="s">
         <v>1012</v>
@@ -18913,7 +18923,7 @@
         <v>705</v>
       </c>
       <c r="CH52" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="CI52" t="s">
         <v>944</v>
@@ -18952,7 +18962,7 @@
         <v>708949699</v>
       </c>
       <c r="YF52" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="YG52" s="1">
         <v>46108.648784722223</v>
@@ -18964,7 +18974,7 @@
         <v>1076</v>
       </c>
       <c r="YN52" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="YO52">
         <v>51</v>
@@ -18978,10 +18988,10 @@
         <v>46108.693661307872</v>
       </c>
       <c r="D53" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E53" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F53" s="1">
         <v>46105</v>
@@ -19032,7 +19042,7 @@
         <v>1043</v>
       </c>
       <c r="AI53" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AJ53" t="s">
         <v>999</v>
@@ -19074,7 +19084,7 @@
         <v>674</v>
       </c>
       <c r="AY53" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AZ53" t="s">
         <v>719</v>
@@ -19104,16 +19114,16 @@
         <v>687</v>
       </c>
       <c r="BI53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="BJ53" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="BK53" t="s">
         <v>809</v>
       </c>
       <c r="BL53" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="BM53" t="s">
         <v>936</v>
@@ -19122,22 +19132,22 @@
         <v>893</v>
       </c>
       <c r="BO53" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="BP53" t="s">
         <v>851</v>
       </c>
       <c r="BR53" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="BS53" t="s">
         <v>881</v>
       </c>
       <c r="BT53" t="s">
+        <v>1484</v>
+      </c>
+      <c r="BU53" t="s">
         <v>1485</v>
-      </c>
-      <c r="BU53" t="s">
-        <v>1486</v>
       </c>
       <c r="CA53" t="s">
         <v>702</v>
@@ -19155,7 +19165,7 @@
         <v>754</v>
       </c>
       <c r="CK53" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="CM53" t="s">
         <v>758</v>
@@ -19167,7 +19177,7 @@
         <v>708953564</v>
       </c>
       <c r="YF53" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="YG53" s="1">
         <v>46108.652002314811</v>
@@ -19179,7 +19189,7 @@
         <v>1076</v>
       </c>
       <c r="YN53" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="YO53">
         <v>52</v>
@@ -19193,10 +19203,10 @@
         <v>46108.69771064815</v>
       </c>
       <c r="D54" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E54" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F54" s="1">
         <v>46105</v>
@@ -19235,16 +19245,16 @@
         <v>674</v>
       </c>
       <c r="T54" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="U54" t="s">
         <v>1062</v>
       </c>
       <c r="V54" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="X54" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="Y54" t="s">
         <v>1062</v>
@@ -19268,7 +19278,7 @@
         <v>3</v>
       </c>
       <c r="AO54" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="AP54">
         <v>1</v>
@@ -19289,7 +19299,7 @@
         <v>1</v>
       </c>
       <c r="AV54" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="AX54" t="s">
         <v>968</v>
@@ -19319,31 +19329,31 @@
         <v>1083</v>
       </c>
       <c r="BI54" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="BJ54" t="s">
+        <v>1192</v>
+      </c>
+      <c r="BM54" t="s">
         <v>1193</v>
       </c>
-      <c r="BM54" t="s">
-        <v>1194</v>
-      </c>
       <c r="BN54" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="BR54" t="s">
         <v>695</v>
       </c>
       <c r="BS54" t="s">
+        <v>1494</v>
+      </c>
+      <c r="BT54" t="s">
         <v>1495</v>
       </c>
-      <c r="BT54" t="s">
+      <c r="BU54" t="s">
+        <v>1199</v>
+      </c>
+      <c r="BV54" t="s">
         <v>1496</v>
-      </c>
-      <c r="BU54" t="s">
-        <v>1200</v>
-      </c>
-      <c r="BV54" t="s">
-        <v>1497</v>
       </c>
       <c r="CA54" t="s">
         <v>801</v>
@@ -19376,13 +19386,13 @@
         <v>671</v>
       </c>
       <c r="DN54" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="YE54">
         <v>708958410</v>
       </c>
       <c r="YF54" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="YG54" s="1">
         <v>46108.656041666669</v>
@@ -19394,7 +19404,7 @@
         <v>1076</v>
       </c>
       <c r="YN54" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="YO54">
         <v>53</v>
@@ -19408,10 +19418,10 @@
         <v>46108.701265138887</v>
       </c>
       <c r="D55" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E55" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="F55" s="1">
         <v>46105</v>
@@ -19495,7 +19505,7 @@
         <v>866</v>
       </c>
       <c r="AY55" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="AZ55" t="s">
         <v>1079</v>
@@ -19525,43 +19535,43 @@
         <v>950</v>
       </c>
       <c r="BI55" t="s">
+        <v>1501</v>
+      </c>
+      <c r="BJ55" t="s">
         <v>1502</v>
       </c>
-      <c r="BJ55" t="s">
+      <c r="BK55" t="s">
         <v>1503</v>
       </c>
-      <c r="BK55" t="s">
+      <c r="BL55" t="s">
         <v>1504</v>
-      </c>
-      <c r="BL55" t="s">
-        <v>1505</v>
       </c>
       <c r="BM55" t="s">
         <v>915</v>
       </c>
       <c r="BN55" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="BO55" t="s">
         <v>936</v>
       </c>
       <c r="BP55" t="s">
+        <v>1506</v>
+      </c>
+      <c r="BQ55" t="s">
+        <v>1322</v>
+      </c>
+      <c r="BR55" t="s">
+        <v>1175</v>
+      </c>
+      <c r="BS55" t="s">
         <v>1507</v>
-      </c>
-      <c r="BQ55" t="s">
-        <v>1323</v>
-      </c>
-      <c r="BR55" t="s">
-        <v>1176</v>
-      </c>
-      <c r="BS55" t="s">
-        <v>1508</v>
       </c>
       <c r="BT55" t="s">
         <v>853</v>
       </c>
       <c r="BU55" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="BV55" t="s">
         <v>719</v>
@@ -19570,7 +19580,7 @@
         <v>705</v>
       </c>
       <c r="CB55" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="CC55" t="s">
         <v>700</v>
@@ -19618,7 +19628,7 @@
         <v>708962558</v>
       </c>
       <c r="YF55" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="YG55" s="1">
         <v>46108.65960648148</v>
@@ -19630,7 +19640,7 @@
         <v>1076</v>
       </c>
       <c r="YN55" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="YO55">
         <v>54</v>
@@ -19644,10 +19654,10 @@
         <v>46108.70485425926</v>
       </c>
       <c r="D56" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E56" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="F56" s="1">
         <v>46105</v>
@@ -19692,7 +19702,7 @@
         <v>671</v>
       </c>
       <c r="AG56" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AH56" t="s">
         <v>1043</v>
@@ -19713,7 +19723,7 @@
         <v>3</v>
       </c>
       <c r="AO56" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="AP56">
         <v>0</v>
@@ -19743,10 +19753,10 @@
         <v>679</v>
       </c>
       <c r="AZ56" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="BA56" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="BB56" t="s">
         <v>822</v>
@@ -19767,7 +19777,7 @@
         <v>683</v>
       </c>
       <c r="BH56" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="BI56" t="s">
         <v>934</v>
@@ -19779,19 +19789,19 @@
         <v>953</v>
       </c>
       <c r="BL56" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="BM56" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="BN56" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="BO56" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="BP56" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="BQ56" t="s">
         <v>893</v>
@@ -19806,7 +19816,7 @@
         <v>1012</v>
       </c>
       <c r="BU56" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="BV56" t="s">
         <v>1031</v>
@@ -19845,7 +19855,7 @@
         <v>705</v>
       </c>
       <c r="CV56" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="CW56" t="s">
         <v>758</v>
@@ -19857,7 +19867,7 @@
         <v>708966848</v>
       </c>
       <c r="YF56" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="YG56" s="1">
         <v>46108.663194444453</v>
@@ -19869,7 +19879,7 @@
         <v>1076</v>
       </c>
       <c r="YN56" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="YO56">
         <v>55</v>
@@ -19883,10 +19893,10 @@
         <v>46108.707650775461</v>
       </c>
       <c r="D57" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E57" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="F57" s="1">
         <v>46105</v>
@@ -19931,16 +19941,16 @@
         <v>671</v>
       </c>
       <c r="AG57" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="AH57" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="AI57" t="s">
         <v>948</v>
       </c>
       <c r="AJ57" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="AK57">
         <v>5</v>
@@ -20003,19 +20013,19 @@
         <v>985</v>
       </c>
       <c r="BH57" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="BI57" t="s">
         <v>871</v>
       </c>
       <c r="BJ57" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="BK57" t="s">
         <v>969</v>
       </c>
       <c r="BL57" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="BM57" t="s">
         <v>936</v>
@@ -20024,46 +20034,46 @@
         <v>955</v>
       </c>
       <c r="BO57" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="BP57" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="BQ57" t="s">
+        <v>1524</v>
+      </c>
+      <c r="BR57" t="s">
         <v>1525</v>
-      </c>
-      <c r="BR57" t="s">
-        <v>1526</v>
       </c>
       <c r="BS57" t="s">
         <v>747</v>
       </c>
       <c r="BT57" t="s">
+        <v>1526</v>
+      </c>
+      <c r="BU57" t="s">
         <v>1527</v>
       </c>
-      <c r="BU57" t="s">
-        <v>1528</v>
-      </c>
       <c r="BV57" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="CA57" t="s">
         <v>705</v>
       </c>
       <c r="CB57" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="CC57" t="s">
         <v>705</v>
       </c>
       <c r="CD57" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="YE57">
         <v>708969971</v>
       </c>
       <c r="YF57" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="YG57" s="1">
         <v>46108.665983796287</v>
@@ -20075,7 +20085,7 @@
         <v>1076</v>
       </c>
       <c r="YN57" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="YO57">
         <v>56</v>
@@ -20089,10 +20099,10 @@
         <v>46108.712396724542</v>
       </c>
       <c r="D58" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E58" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="F58" s="1">
         <v>46105</v>
@@ -20137,7 +20147,7 @@
         <v>671</v>
       </c>
       <c r="AG58" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AH58" t="s">
         <v>1043</v>
@@ -20146,7 +20156,7 @@
         <v>966</v>
       </c>
       <c r="AJ58" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="AK58">
         <v>5</v>
@@ -20197,7 +20207,7 @@
         <v>683</v>
       </c>
       <c r="BF58" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="BG58" t="s">
         <v>985</v>
@@ -20206,13 +20216,13 @@
         <v>687</v>
       </c>
       <c r="BI58" t="s">
+        <v>1534</v>
+      </c>
+      <c r="BJ58" t="s">
         <v>1535</v>
       </c>
-      <c r="BJ58" t="s">
+      <c r="BK58" t="s">
         <v>1536</v>
-      </c>
-      <c r="BK58" t="s">
-        <v>1537</v>
       </c>
       <c r="BL58" t="s">
         <v>1036</v>
@@ -20227,10 +20237,10 @@
         <v>851</v>
       </c>
       <c r="BP58" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="BQ58" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="BR58" t="s">
         <v>939</v>
@@ -20239,7 +20249,7 @@
         <v>747</v>
       </c>
       <c r="BT58" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="BU58" t="s">
         <v>993</v>
@@ -20257,7 +20267,7 @@
         <v>702</v>
       </c>
       <c r="CG58" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="CI58" t="s">
         <v>774</v>
@@ -20266,7 +20276,7 @@
         <v>705</v>
       </c>
       <c r="CL58" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="CM58" t="s">
         <v>734</v>
@@ -20275,7 +20285,7 @@
         <v>705</v>
       </c>
       <c r="CP58" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="CQ58" t="s">
         <v>753</v>
@@ -20287,7 +20297,7 @@
         <v>977</v>
       </c>
       <c r="CW58" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="CY58" t="s">
         <v>707</v>
@@ -20296,7 +20306,7 @@
         <v>705</v>
       </c>
       <c r="DB58" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="DC58" t="s">
         <v>708</v>
@@ -20305,13 +20315,13 @@
         <v>671</v>
       </c>
       <c r="DN58" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="YE58">
         <v>708975644</v>
       </c>
       <c r="YF58" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="YG58" s="1">
         <v>46108.670729166668</v>
@@ -20323,7 +20333,7 @@
         <v>1076</v>
       </c>
       <c r="YN58" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="YO58">
         <v>57</v>
@@ -20337,10 +20347,10 @@
         <v>46108.742514953701</v>
       </c>
       <c r="D59" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E59" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="F59" s="1">
         <v>46105</v>
@@ -20385,7 +20395,7 @@
         <v>671</v>
       </c>
       <c r="AG59" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="AH59" t="s">
         <v>682</v>
@@ -20406,7 +20416,7 @@
         <v>5</v>
       </c>
       <c r="AO59" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="AP59">
         <v>1</v>
@@ -20427,7 +20437,7 @@
         <v>1</v>
       </c>
       <c r="AV59" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="AW59" t="s">
         <v>676</v>
@@ -20445,28 +20455,28 @@
         <v>866</v>
       </c>
       <c r="BB59" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="BC59" t="s">
         <v>683</v>
       </c>
       <c r="BD59" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="BE59" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="BF59" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="BG59" t="s">
         <v>949</v>
       </c>
       <c r="BH59" t="s">
+        <v>1550</v>
+      </c>
+      <c r="BI59" t="s">
         <v>1551</v>
-      </c>
-      <c r="BI59" t="s">
-        <v>1552</v>
       </c>
       <c r="BM59" t="s">
         <v>915</v>
@@ -20475,25 +20485,25 @@
         <v>852</v>
       </c>
       <c r="BO59" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="BP59" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="BR59" t="s">
+        <v>1552</v>
+      </c>
+      <c r="BS59" t="s">
         <v>1553</v>
       </c>
-      <c r="BS59" t="s">
+      <c r="BT59" t="s">
         <v>1554</v>
       </c>
-      <c r="BT59" t="s">
+      <c r="BU59" t="s">
         <v>1555</v>
       </c>
-      <c r="BU59" t="s">
+      <c r="BV59" t="s">
         <v>1556</v>
-      </c>
-      <c r="BV59" t="s">
-        <v>1557</v>
       </c>
       <c r="CA59" t="s">
         <v>701</v>
@@ -20502,10 +20512,10 @@
         <v>705</v>
       </c>
       <c r="CD59" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="CE59" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="CG59" t="s">
         <v>705</v>
@@ -20517,19 +20527,19 @@
         <v>705</v>
       </c>
       <c r="CJ59" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="CK59" t="s">
         <v>705</v>
       </c>
       <c r="CL59" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="CM59" t="s">
         <v>705</v>
       </c>
       <c r="CN59" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="CO59" t="s">
         <v>733</v>
@@ -20541,7 +20551,7 @@
         <v>705</v>
       </c>
       <c r="CT59" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="CU59" t="s">
         <v>699</v>
@@ -20550,34 +20560,34 @@
         <v>705</v>
       </c>
       <c r="CX59" t="s">
+        <v>1562</v>
+      </c>
+      <c r="CY59" t="s">
         <v>1563</v>
-      </c>
-      <c r="CY59" t="s">
-        <v>1564</v>
       </c>
       <c r="DA59" t="s">
         <v>705</v>
       </c>
       <c r="DB59" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="DC59" t="s">
         <v>705</v>
       </c>
       <c r="DD59" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="DM59" t="s">
         <v>671</v>
       </c>
       <c r="DN59" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="YE59">
         <v>708981587</v>
       </c>
       <c r="YF59" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="YG59" s="1">
         <v>46108.676076388889</v>
@@ -20589,7 +20599,7 @@
         <v>1076</v>
       </c>
       <c r="YN59" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="YO59">
         <v>58</v>
@@ -20603,10 +20613,10 @@
         <v>46108.721968414349</v>
       </c>
       <c r="D60" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E60" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="F60" s="1">
         <v>46105</v>
@@ -20651,7 +20661,7 @@
         <v>671</v>
       </c>
       <c r="AG60" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AH60" t="s">
         <v>746</v>
@@ -20660,7 +20670,7 @@
         <v>1046</v>
       </c>
       <c r="AJ60" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="AK60">
         <v>5</v>
@@ -20672,7 +20682,7 @@
         <v>7</v>
       </c>
       <c r="AO60" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AP60">
         <v>1</v>
@@ -20696,7 +20706,7 @@
         <v>737</v>
       </c>
       <c r="AX60" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AY60" t="s">
         <v>1043</v>
@@ -20729,31 +20739,31 @@
         <v>687</v>
       </c>
       <c r="BI60" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="BJ60" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="BK60" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="BL60" t="s">
         <v>1083</v>
       </c>
       <c r="BM60" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="BN60" t="s">
         <v>955</v>
       </c>
       <c r="BO60" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="BP60" t="s">
         <v>936</v>
       </c>
       <c r="BQ60" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="BR60" t="s">
         <v>938</v>
@@ -20765,58 +20775,58 @@
         <v>747</v>
       </c>
       <c r="BU60" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="BV60" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="CA60" t="s">
         <v>705</v>
       </c>
       <c r="CB60" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="CC60" t="s">
         <v>705</v>
       </c>
       <c r="CD60" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="CE60" t="s">
         <v>705</v>
       </c>
       <c r="CF60" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="CG60" t="s">
         <v>705</v>
       </c>
       <c r="CH60" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="CI60" t="s">
         <v>705</v>
       </c>
       <c r="CJ60" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="CK60" t="s">
         <v>705</v>
       </c>
       <c r="CL60" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="DM60" t="s">
         <v>671</v>
       </c>
       <c r="DN60" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="YE60">
         <v>708986371</v>
       </c>
       <c r="YF60" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="YG60" s="1">
         <v>46108.680300925917</v>
@@ -20828,7 +20838,7 @@
         <v>1076</v>
       </c>
       <c r="YN60" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="YO60">
         <v>59</v>
@@ -20842,10 +20852,10 @@
         <v>46108.726186203698</v>
       </c>
       <c r="D61" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E61" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F61" s="1">
         <v>46105</v>
@@ -20887,13 +20897,13 @@
         <v>1062</v>
       </c>
       <c r="U61" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="X61" t="s">
         <v>1062</v>
       </c>
       <c r="Y61" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AB61" t="s">
         <v>736</v>
@@ -20983,13 +20993,13 @@
         <v>891</v>
       </c>
       <c r="BJ61" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="BK61" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="BL61" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="BM61" t="s">
         <v>851</v>
@@ -21001,28 +21011,28 @@
         <v>955</v>
       </c>
       <c r="BP61" t="s">
+        <v>1585</v>
+      </c>
+      <c r="BQ61" t="s">
         <v>1586</v>
       </c>
-      <c r="BQ61" t="s">
-        <v>1587</v>
-      </c>
       <c r="BR61" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="BS61" t="s">
         <v>881</v>
       </c>
       <c r="BT61" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="BU61" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="BV61" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="CA61" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="CC61" t="s">
         <v>699</v>
@@ -21031,7 +21041,7 @@
         <v>705</v>
       </c>
       <c r="CF61" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="CG61" t="s">
         <v>756</v>
@@ -21043,7 +21053,7 @@
         <v>705</v>
       </c>
       <c r="CL61" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="CM61" t="s">
         <v>703</v>
@@ -21064,7 +21074,7 @@
         <v>708991906</v>
       </c>
       <c r="YF61" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="YG61" s="1">
         <v>46108.684525462973</v>
@@ -21076,7 +21086,7 @@
         <v>1076</v>
       </c>
       <c r="YN61" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="YO61">
         <v>60</v>
@@ -21090,10 +21100,10 @@
         <v>46108.729913564814</v>
       </c>
       <c r="D62" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E62" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F62" s="1">
         <v>46105</v>
@@ -21135,13 +21145,13 @@
         <v>1062</v>
       </c>
       <c r="U62" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="X62" t="s">
         <v>1062</v>
       </c>
       <c r="Y62" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="AB62" t="s">
         <v>736</v>
@@ -21171,7 +21181,7 @@
         <v>4</v>
       </c>
       <c r="AO62" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="AP62">
         <v>0</v>
@@ -21228,7 +21238,7 @@
         <v>687</v>
       </c>
       <c r="BI62" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="BJ62" t="s">
         <v>891</v>
@@ -21246,16 +21256,16 @@
         <v>915</v>
       </c>
       <c r="BO62" t="s">
+        <v>1594</v>
+      </c>
+      <c r="BP62" t="s">
         <v>1595</v>
       </c>
-      <c r="BP62" t="s">
-        <v>1596</v>
-      </c>
       <c r="BQ62" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="BR62" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="BS62" t="s">
         <v>747</v>
@@ -21267,7 +21277,7 @@
         <v>1036</v>
       </c>
       <c r="BV62" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="CA62" t="s">
         <v>700</v>
@@ -21294,7 +21304,7 @@
         <v>705</v>
       </c>
       <c r="CP62" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="CQ62" t="s">
         <v>977</v>
@@ -21309,7 +21319,7 @@
         <v>708996502</v>
       </c>
       <c r="YF62" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="YG62" s="1">
         <v>46108.688252314823</v>
@@ -21321,13 +21331,14 @@
         <v>1076</v>
       </c>
       <c r="YN62" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="YO62">
         <v>61</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>